--- a/PRIZEPICKS_HITTER_AI_V3_TOP30_2026_07_12.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V3_TOP30_2026_07_12.xlsx
@@ -1989,13 +1989,13 @@
         <v>1.03</v>
       </c>
       <c r="BC4" s="3" t="n">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="BD4" s="3" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF4" s="3" t="n">
         <v>6</v>
@@ -2331,13 +2331,13 @@
         <v>1.03</v>
       </c>
       <c r="BC5" s="3" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="BD5" s="3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" s="3" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="BF5" s="3" t="n">
         <v>8</v>
@@ -2673,13 +2673,13 @@
         <v>1.01</v>
       </c>
       <c r="BC6" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD6" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE6" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF6" s="3" t="n">
         <v>2</v>
@@ -3015,13 +3015,13 @@
         <v>1.01</v>
       </c>
       <c r="BC7" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD7" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE7" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF7" s="3" t="n">
         <v>2</v>
@@ -3357,13 +3357,13 @@
         <v>1.01</v>
       </c>
       <c r="BC8" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD8" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE8" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF8" s="3" t="n">
         <v>2</v>
@@ -4033,13 +4033,13 @@
         <v>1.03</v>
       </c>
       <c r="BC10" s="3" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="BD10" s="3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE10" s="3" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="BF10" s="3" t="n">
         <v>8</v>
@@ -4709,13 +4709,13 @@
         <v>1.03</v>
       </c>
       <c r="BC12" s="3" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="BD12" s="3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BE12" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="BF12" s="3" t="n">
         <v>1</v>
@@ -5051,13 +5051,13 @@
         <v>1.03</v>
       </c>
       <c r="BC13" s="3" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="BD13" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BF13" s="3" t="n">
         <v>0</v>
@@ -5393,13 +5393,13 @@
         <v>1.03</v>
       </c>
       <c r="BC14" s="3" t="n">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="BD14" s="3" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF14" s="3" t="n">
         <v>6</v>
@@ -6403,13 +6403,13 @@
         <v>1.01</v>
       </c>
       <c r="BC17" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD17" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF17" s="3" t="n">
         <v>2</v>
@@ -6745,13 +6745,13 @@
         <v>1.03</v>
       </c>
       <c r="BC18" s="3" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="BD18" s="3" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="BE18" s="3" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF18" s="3" t="n">
         <v>4</v>
@@ -7087,13 +7087,13 @@
         <v>1</v>
       </c>
       <c r="BC19" s="3" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="BD19" s="3" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="BE19" s="3" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="BF19" s="3" t="n">
         <v>2</v>
@@ -7429,13 +7429,13 @@
         <v>1.03</v>
       </c>
       <c r="BC20" s="3" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="BD20" s="3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" s="3" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="BF20" s="3" t="n">
         <v>8</v>
@@ -7771,13 +7771,13 @@
         <v>1.03</v>
       </c>
       <c r="BC21" s="3" t="n">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="BD21" s="3" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE21" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF21" s="3" t="n">
         <v>6</v>
@@ -8781,13 +8781,13 @@
         <v>1.03</v>
       </c>
       <c r="BC24" s="3" t="n">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="BD24" s="3" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE24" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF24" s="3" t="n">
         <v>6</v>
@@ -9457,13 +9457,13 @@
         <v>1.01</v>
       </c>
       <c r="BC26" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD26" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE26" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF26" s="3" t="n">
         <v>2</v>
@@ -9799,13 +9799,13 @@
         <v>1.01</v>
       </c>
       <c r="BC27" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD27" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE27" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF27" s="3" t="n">
         <v>2</v>
@@ -10475,13 +10475,13 @@
         <v>1.01</v>
       </c>
       <c r="BC29" s="3" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="BD29" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF29" s="3" t="n">
         <v>2</v>
@@ -11151,13 +11151,13 @@
         <v>1.055</v>
       </c>
       <c r="BC31" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="BD31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="BF31" s="3" t="n">
         <v>0</v>

--- a/PRIZEPICKS_HITTER_AI_V3_TOP30_2026_07_12.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V3_TOP30_2026_07_12.xlsx
@@ -1175,22 +1175,22 @@
         <v>12.7</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>13.14</v>
+        <v>13.2</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>74.7</v>
@@ -1199,31 +1199,31 @@
         <v>74.7</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="T2" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="U2" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="W2" s="5" t="n">
-        <v>60.2</v>
+        <v>60.8</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>60.2</v>
+        <v>60.8</v>
       </c>
       <c r="Y2" s="6" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="Z2" s="7" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>308.01</v>
+        <v>308.56</v>
       </c>
       <c r="AB2" s="4" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AC2" s="8" t="inlineStr">
         <is>
-          <t>Forecast 12.7 FS | Sim 13.1</t>
+          <t>Forecast 12.7 FS | Sim 13.2</t>
         </is>
       </c>
       <c r="AD2" s="3" t="n">
@@ -1240,10 +1240,12 @@
       </c>
       <c r="AE2" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF2" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG2" s="3" t="n">
         <v>2</v>
       </c>
@@ -1419,7 +1421,7 @@
         <v>11</v>
       </c>
       <c r="CK2" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="CL2" s="3" t="n">
         <v>5</v>
@@ -1477,87 +1479,87 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>HOU @ TEX</t>
+          <t>CHC @ CIN</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>11.99</v>
+        <v>11.37</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>13.14</v>
+        <v>11.65</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>89.2</v>
+        <v>87.2</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>63.1</v>
+        <v>58.6</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="W3" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="X3" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="Y3" s="6" t="n">
-        <v>54.9</v>
+        <v>58.6</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="X3" s="7" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="Y3" s="7" t="n">
+        <v>50.1</v>
       </c>
       <c r="Z3" s="7" t="n">
-        <v>54.9</v>
+        <v>50.1</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>283.81</v>
+        <v>284.43</v>
       </c>
       <c r="AB3" s="4" t="inlineStr">
         <is>
@@ -1566,7 +1568,7 @@
       </c>
       <c r="AC3" s="8" t="inlineStr">
         <is>
-          <t>Forecast 12.0 FS | Sim 13.1</t>
+          <t>Forecast 11.4 FS | Sim 11.7</t>
         </is>
       </c>
       <c r="AD3" s="3" t="n">
@@ -1574,26 +1576,28 @@
       </c>
       <c r="AE3" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI3" s="4" t="inlineStr">
         <is>
-          <t>1-1-1</t>
+          <t>1-1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>100</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
@@ -1601,127 +1605,135 @@
         </is>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO3" s="4" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="AP3" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>10.22</v>
+        <v>3.92</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>0.254</v>
+        <v>0.2215</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>0.0476</v>
+        <v>0.0365</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.1027</v>
       </c>
       <c r="AV3" s="3" t="n">
-        <v>4.79</v>
+        <v>4.48</v>
       </c>
       <c r="AW3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AX3" s="3" t="n">
-        <v>0.2086</v>
+        <v>0.2126</v>
       </c>
       <c r="AY3" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0341</v>
       </c>
       <c r="AZ3" s="4" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BA3" s="3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BB3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n"/>
+        <v>1.03</v>
+      </c>
+      <c r="BC3" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="BD3" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE3" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="BF3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="BG3" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="BH3" s="3" t="n">
-        <v>291</v>
+        <v>413</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>248</v>
+        <v>355</v>
       </c>
       <c r="BJ3" s="3" t="n">
-        <v>0.234</v>
+        <v>0.29</v>
       </c>
       <c r="BK3" s="3" t="n">
-        <v>0.334</v>
+        <v>0.383</v>
       </c>
       <c r="BL3" s="3" t="n">
-        <v>0.46</v>
+        <v>0.532</v>
       </c>
       <c r="BM3" s="3" t="n">
-        <v>0.794</v>
+        <v>0.915</v>
       </c>
       <c r="BN3" s="3" t="n">
-        <v>267</v>
+        <v>137</v>
       </c>
       <c r="BO3" s="3" t="n">
-        <v>0.797</v>
+        <v>0.865</v>
       </c>
       <c r="BP3" s="3" t="n">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="BQ3" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BR3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BS3" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BT3" s="3" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="BU3" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="BV3" s="3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="BW3" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BX3" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="BY3" s="3" t="n">
-        <v>4.71</v>
+        <v>11.71</v>
       </c>
       <c r="BZ3" s="3" t="n">
-        <v>8.57</v>
+        <v>11.93</v>
       </c>
       <c r="CA3" s="3" t="n">
-        <v>0.239</v>
+        <v>0.292</v>
       </c>
       <c r="CB3" s="4" t="inlineStr">
         <is>
@@ -1729,71 +1741,71 @@
         </is>
       </c>
       <c r="CC3" s="3" t="n">
-        <v>6.27</v>
+        <v>13.43</v>
       </c>
       <c r="CD3" s="3" t="n">
-        <v>2.308</v>
+        <v>2.651</v>
       </c>
       <c r="CE3" s="3" t="n">
-        <v>0.2115</v>
+        <v>0.2222</v>
       </c>
       <c r="CF3" s="3" t="n">
-        <v>0.1154</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="CG3" s="3" t="n">
-        <v>0.1154</v>
+        <v>0.0635</v>
       </c>
       <c r="CH3" s="3" t="n">
-        <v>0.1154</v>
+        <v>0.2063</v>
       </c>
       <c r="CI3" s="3" t="n">
-        <v>0.0192</v>
+        <v>0.0794</v>
       </c>
       <c r="CJ3" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CK3" s="3" t="n">
-        <v>9.83</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="CL3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="CM3" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CN3" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CO3" s="3" t="n">
-        <v>0.1639</v>
+        <v>0.1487</v>
       </c>
       <c r="CP3" s="3" t="n">
-        <v>0.0414</v>
+        <v>0.0427</v>
       </c>
       <c r="CQ3" s="3" t="n">
-        <v>0.0056</v>
+        <v>0.0059</v>
       </c>
       <c r="CR3" s="3" t="n">
-        <v>0.078</v>
+        <v>0.0553</v>
       </c>
       <c r="CS3" s="3" t="n">
-        <v>0.1396</v>
+        <v>0.1379</v>
       </c>
       <c r="CT3" s="3" t="n">
-        <v>0.0134</v>
+        <v>0.0222</v>
       </c>
       <c r="CU3" s="3" t="n">
-        <v>0.1371</v>
+        <v>0.1426</v>
       </c>
       <c r="CV3" s="3" t="n">
-        <v>0.1125</v>
+        <v>0.1024</v>
       </c>
       <c r="CW3" s="3" t="n">
-        <v>0.0097</v>
+        <v>0.0295</v>
       </c>
       <c r="CX3" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1811,87 +1823,87 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>CHC @ CIN</t>
+          <t>NYY @ WSH</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>11.37</v>
+        <v>10.86</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>11.57</v>
+        <v>10.86</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>86.5</v>
+        <v>84</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>76.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>76.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>64.7</v>
+        <v>61</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>64.7</v>
+        <v>61</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>57.8</v>
+        <v>53.7</v>
       </c>
       <c r="V4" s="7" t="n">
-        <v>57.8</v>
+        <v>53.7</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>53.7</v>
+        <v>50.2</v>
       </c>
       <c r="X4" s="7" t="n">
-        <v>53.7</v>
+        <v>50.2</v>
       </c>
       <c r="Y4" s="7" t="n">
-        <v>49</v>
+        <v>45.9</v>
       </c>
       <c r="Z4" s="7" t="n">
-        <v>49</v>
+        <v>45.9</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>283.58</v>
+        <v>283.71</v>
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
@@ -1900,7 +1912,7 @@
       </c>
       <c r="AC4" s="8" t="inlineStr">
         <is>
-          <t>Forecast 11.4 FS | Sim 11.6</t>
+          <t>Forecast 10.9 FS | Sim 10.9</t>
         </is>
       </c>
       <c r="AD4" s="3" t="n">
@@ -1908,10 +1920,12 @@
       </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF4" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG4" s="3" t="n">
         <v>1</v>
       </c>
@@ -1942,63 +1956,63 @@
       </c>
       <c r="AO4" s="4" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AR4" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS4" s="3" t="n">
-        <v>0.2215</v>
+        <v>0.2366</v>
       </c>
       <c r="AT4" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0317</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>0.1027</v>
+        <v>0.0756</v>
       </c>
       <c r="AV4" s="3" t="n">
-        <v>4.48</v>
+        <v>3.39</v>
       </c>
       <c r="AW4" s="3" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AX4" s="3" t="n">
-        <v>0.2126</v>
+        <v>0.2047</v>
       </c>
       <c r="AY4" s="3" t="n">
-        <v>0.0341</v>
+        <v>0.027</v>
       </c>
       <c r="AZ4" s="4" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BA4" s="3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BB4" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="BC4" s="3" t="n">
-        <v>81.8</v>
+        <v>83.2</v>
       </c>
       <c r="BD4" s="3" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="BE4" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BF4" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BG4" s="4" t="inlineStr">
         <is>
@@ -2006,132 +2020,132 @@
         </is>
       </c>
       <c r="BH4" s="3" t="n">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="BJ4" s="3" t="n">
-        <v>0.29</v>
+        <v>0.278</v>
       </c>
       <c r="BK4" s="3" t="n">
-        <v>0.383</v>
+        <v>0.407</v>
       </c>
       <c r="BL4" s="3" t="n">
-        <v>0.532</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="BM4" s="3" t="n">
-        <v>0.915</v>
+        <v>0.974</v>
       </c>
       <c r="BN4" s="3" t="n">
-        <v>137</v>
+        <v>300</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>0.865</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BQ4" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="BU4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="BV4" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="BR4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS4" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT4" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="BU4" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="BV4" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="BW4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX4" s="3" t="n">
-        <v>23</v>
-      </c>
       <c r="BY4" s="3" t="n">
-        <v>11.71</v>
+        <v>19.86</v>
       </c>
       <c r="BZ4" s="3" t="n">
-        <v>11.93</v>
+        <v>16.29</v>
       </c>
       <c r="CA4" s="3" t="n">
-        <v>0.292</v>
+        <v>0.385</v>
       </c>
       <c r="CB4" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="CC4" s="3" t="n">
-        <v>13.43</v>
+        <v>12.53</v>
       </c>
       <c r="CD4" s="3" t="n">
-        <v>2.651</v>
+        <v>3.353</v>
       </c>
       <c r="CE4" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.2941</v>
       </c>
       <c r="CF4" s="3" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1765</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>0.0635</v>
+        <v>0.1029</v>
       </c>
       <c r="CH4" s="3" t="n">
-        <v>0.2063</v>
+        <v>0.2353</v>
       </c>
       <c r="CI4" s="3" t="n">
-        <v>0.0794</v>
+        <v>0.0294</v>
       </c>
       <c r="CJ4" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CK4" s="3" t="n">
-        <v>8.94</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="CL4" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM4" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CN4" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CO4" s="3" t="n">
-        <v>0.1487</v>
+        <v>0.1259</v>
       </c>
       <c r="CP4" s="3" t="n">
-        <v>0.0427</v>
+        <v>0.0498</v>
       </c>
       <c r="CQ4" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.0042</v>
       </c>
       <c r="CR4" s="3" t="n">
-        <v>0.0553</v>
+        <v>0.0524</v>
       </c>
       <c r="CS4" s="3" t="n">
-        <v>0.1379</v>
+        <v>0.1323</v>
       </c>
       <c r="CT4" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="CU4" s="3" t="n">
-        <v>0.1426</v>
+        <v>0.1632</v>
       </c>
       <c r="CV4" s="3" t="n">
-        <v>0.1024</v>
+        <v>0.116</v>
       </c>
       <c r="CW4" s="3" t="n">
-        <v>0.0295</v>
+        <v>0.0189</v>
       </c>
       <c r="CX4" s="4" t="inlineStr">
         <is>
@@ -2153,22 +2167,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>NYY @ WSH</t>
+          <t>HOU @ TEX</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -2178,62 +2192,62 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>10.86</v>
+        <v>11.99</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10.72</v>
+        <v>12.99</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>78.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>78.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>72.8</v>
+        <v>80.3</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>72.8</v>
+        <v>80.3</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>64.3</v>
+        <v>72.5</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>64.3</v>
+        <v>72.5</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>60.7</v>
+        <v>69</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="V5" s="7" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="X5" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="Y5" s="7" t="n">
-        <v>44.9</v>
+        <v>69</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>55</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>44.9</v>
+        <v>55</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>282.65</v>
+        <v>282.71</v>
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
@@ -2242,7 +2256,7 @@
       </c>
       <c r="AC5" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.9 FS | Sim 10.7</t>
+          <t>Forecast 12.0 FS | Sim 13.0</t>
         </is>
       </c>
       <c r="AD5" s="3" t="n">
@@ -2250,26 +2264,28 @@
       </c>
       <c r="AE5" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF5" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AI5" s="4" t="inlineStr">
         <is>
-          <t>1-1-1-1-1-1-1</t>
+          <t>1-1-1</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>100</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
@@ -2277,14 +2293,14 @@
         </is>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN5" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO5" s="4" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="AP5" s="4" t="inlineStr">
@@ -2293,191 +2309,183 @@
         </is>
       </c>
       <c r="AQ5" s="3" t="n">
-        <v>4.15</v>
+        <v>10.22</v>
       </c>
       <c r="AR5" s="3" t="n">
-        <v>1.37</v>
+        <v>2.27</v>
       </c>
       <c r="AS5" s="3" t="n">
-        <v>0.2366</v>
+        <v>0.254</v>
       </c>
       <c r="AT5" s="3" t="n">
-        <v>0.0317</v>
+        <v>0.0476</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>0.0756</v>
+        <v>0.1905</v>
       </c>
       <c r="AV5" s="3" t="n">
-        <v>3.39</v>
+        <v>4.79</v>
       </c>
       <c r="AW5" s="3" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AX5" s="3" t="n">
-        <v>0.2047</v>
+        <v>0.2086</v>
       </c>
       <c r="AY5" s="3" t="n">
-        <v>0.027</v>
+        <v>0.0365</v>
       </c>
       <c r="AZ5" s="4" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BA5" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BB5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="BB5" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC5" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="BD5" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE5" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="BF5" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="BC5" s="4" t="n"/>
+      <c r="BD5" s="4" t="n"/>
+      <c r="BE5" s="4" t="n"/>
+      <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="BH5" s="3" t="n">
-        <v>450</v>
+        <v>291</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>367</v>
+        <v>248</v>
       </c>
       <c r="BJ5" s="3" t="n">
-        <v>0.278</v>
+        <v>0.234</v>
       </c>
       <c r="BK5" s="3" t="n">
-        <v>0.407</v>
+        <v>0.334</v>
       </c>
       <c r="BL5" s="3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="BM5" s="3" t="n">
-        <v>0.974</v>
+        <v>0.794</v>
       </c>
       <c r="BN5" s="3" t="n">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="BO5" s="3" t="n">
-        <v>1.01</v>
+        <v>0.797</v>
       </c>
       <c r="BP5" s="3" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="BQ5" s="3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BR5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT5" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="BU5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BV5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="BS5" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BT5" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="BU5" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="BV5" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="BW5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX5" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="BY5" s="3" t="n">
-        <v>19.86</v>
+        <v>4.71</v>
       </c>
       <c r="BZ5" s="3" t="n">
-        <v>16.29</v>
+        <v>8.57</v>
       </c>
       <c r="CA5" s="3" t="n">
-        <v>0.385</v>
+        <v>0.239</v>
       </c>
       <c r="CB5" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="CC5" s="3" t="n">
-        <v>12.53</v>
+        <v>6.27</v>
       </c>
       <c r="CD5" s="3" t="n">
-        <v>3.353</v>
+        <v>2.308</v>
       </c>
       <c r="CE5" s="3" t="n">
-        <v>0.2941</v>
+        <v>0.2115</v>
       </c>
       <c r="CF5" s="3" t="n">
-        <v>0.1765</v>
+        <v>0.1154</v>
       </c>
       <c r="CG5" s="3" t="n">
-        <v>0.1029</v>
+        <v>0.1154</v>
       </c>
       <c r="CH5" s="3" t="n">
-        <v>0.2353</v>
+        <v>0.1154</v>
       </c>
       <c r="CI5" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.0192</v>
       </c>
       <c r="CJ5" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CK5" s="3" t="n">
-        <v>8.73</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="CL5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM5" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CN5" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CO5" s="3" t="n">
-        <v>0.1259</v>
+        <v>0.1639</v>
       </c>
       <c r="CP5" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0414</v>
       </c>
       <c r="CQ5" s="3" t="n">
-        <v>0.0042</v>
+        <v>0.0056</v>
       </c>
       <c r="CR5" s="3" t="n">
-        <v>0.0524</v>
+        <v>0.078</v>
       </c>
       <c r="CS5" s="3" t="n">
-        <v>0.1323</v>
+        <v>0.1396</v>
       </c>
       <c r="CT5" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0134</v>
       </c>
       <c r="CU5" s="3" t="n">
-        <v>0.1632</v>
+        <v>0.1371</v>
       </c>
       <c r="CV5" s="3" t="n">
-        <v>0.116</v>
+        <v>0.1125</v>
       </c>
       <c r="CW5" s="3" t="n">
-        <v>0.0189</v>
+        <v>0.0097</v>
       </c>
       <c r="CX5" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2527,55 +2535,55 @@
         <v>11.16</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.18</v>
+        <v>11.36</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>79.8</v>
+        <v>80.2</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>79.8</v>
+        <v>80.2</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>67.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>67.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>52.4</v>
+        <v>64.5</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>52.6</v>
       </c>
       <c r="X6" s="7" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>277.96</v>
+        <v>279.36</v>
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
@@ -2584,7 +2592,7 @@
       </c>
       <c r="AC6" s="8" t="inlineStr">
         <is>
-          <t>Forecast 11.2 FS | Sim 11.2</t>
+          <t>Forecast 11.2 FS | Sim 11.4</t>
         </is>
       </c>
       <c r="AD6" s="3" t="n">
@@ -2592,10 +2600,12 @@
       </c>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AG6" s="3" t="n">
         <v>4</v>
       </c>
@@ -2673,16 +2683,16 @@
         <v>1.01</v>
       </c>
       <c r="BC6" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD6" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE6" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG6" s="4" t="inlineStr">
         <is>
@@ -2779,7 +2789,7 @@
         <v>9</v>
       </c>
       <c r="CK6" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="CL6" s="3" t="n">
         <v>5</v>
@@ -2788,7 +2798,7 @@
         <v>17</v>
       </c>
       <c r="CN6" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CO6" s="3" t="n">
         <v>0.1808</v>
@@ -2869,34 +2879,34 @@
         <v>10.83</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>11.16</v>
+        <v>11.18</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>63.7</v>
@@ -2905,19 +2915,19 @@
         <v>63.7</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
       <c r="Y7" s="7" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>268.79</v>
+        <v>268.89</v>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
@@ -2934,10 +2944,12 @@
       </c>
       <c r="AE7" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF7" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG7" s="3" t="n">
         <v>2</v>
       </c>
@@ -3015,16 +3027,16 @@
         <v>1.01</v>
       </c>
       <c r="BC7" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD7" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE7" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG7" s="4" t="inlineStr">
         <is>
@@ -3121,13 +3133,13 @@
         <v>10</v>
       </c>
       <c r="CK7" s="3" t="n">
-        <v>7.5</v>
+        <v>7.49</v>
       </c>
       <c r="CL7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="CM7" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CN7" s="3" t="n">
         <v>22</v>
@@ -3211,40 +3223,40 @@
         <v>10.64</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.79</v>
+        <v>10.84</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>63.6</v>
+        <v>63.4</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>63.6</v>
+        <v>63.4</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>57.9</v>
+        <v>57.6</v>
       </c>
       <c r="V8" s="7" t="n">
-        <v>57.9</v>
+        <v>57.6</v>
       </c>
       <c r="W8" s="7" t="n">
         <v>51.4</v>
@@ -3253,13 +3265,13 @@
         <v>51.4</v>
       </c>
       <c r="Y8" s="7" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>261.87</v>
+        <v>262.16</v>
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
@@ -3276,10 +3288,12 @@
       </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF8" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG8" s="3" t="n">
         <v>1</v>
       </c>
@@ -3357,16 +3371,16 @@
         <v>1.01</v>
       </c>
       <c r="BC8" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD8" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE8" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG8" s="4" t="inlineStr">
         <is>
@@ -3463,7 +3477,7 @@
         <v>9</v>
       </c>
       <c r="CK8" s="3" t="n">
-        <v>8.25</v>
+        <v>8.35</v>
       </c>
       <c r="CL8" s="3" t="n">
         <v>5</v>
@@ -3521,87 +3535,87 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HOU @ TEX</t>
+          <t>CHC @ CIN</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>11.03</v>
+        <v>10.44</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>11.54</v>
+        <v>10.45</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>90</v>
+        <v>84.3</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>84</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>84</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>80.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>72.2</v>
+        <v>63.6</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>72.2</v>
+        <v>63.6</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>68.5</v>
+        <v>59.7</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V9" s="5" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>55.7</v>
+        <v>59.7</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="W9" s="7" t="n">
+        <v>48.5</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>55.7</v>
+        <v>48.5</v>
       </c>
       <c r="Y9" s="7" t="n">
-        <v>51.1</v>
+        <v>44</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>51.1</v>
+        <v>44</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>260.71</v>
+        <v>260.14</v>
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
@@ -3610,34 +3624,36 @@
       </c>
       <c r="AC9" s="8" t="inlineStr">
         <is>
-          <t>Forecast 11.0 FS | Sim 11.5</t>
+          <t>Forecast 10.4 FS | Sim 10.4</t>
         </is>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI9" s="4" t="inlineStr">
         <is>
-          <t>3-3-4-3</t>
+          <t>2-4-4-4-3-4</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
@@ -3652,188 +3668,196 @@
       </c>
       <c r="AO9" s="4" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="AP9" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="n">
-        <v>10.22</v>
+        <v>3.92</v>
       </c>
       <c r="AR9" s="3" t="n">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="AS9" s="3" t="n">
-        <v>0.254</v>
+        <v>0.2215</v>
       </c>
       <c r="AT9" s="3" t="n">
-        <v>0.0476</v>
+        <v>0.0365</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.1027</v>
       </c>
       <c r="AV9" s="3" t="n">
-        <v>4.79</v>
+        <v>4.48</v>
       </c>
       <c r="AW9" s="3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AX9" s="3" t="n">
-        <v>0.2086</v>
+        <v>0.2126</v>
       </c>
       <c r="AY9" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0341</v>
       </c>
       <c r="AZ9" s="4" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BA9" s="3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BB9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="n"/>
+        <v>1.03</v>
+      </c>
+      <c r="BC9" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="BD9" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE9" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="BF9" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="BG9" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="BH9" s="3" t="n">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="BJ9" s="3" t="n">
-        <v>0.294</v>
+        <v>0.269</v>
       </c>
       <c r="BK9" s="3" t="n">
-        <v>0.361</v>
+        <v>0.349</v>
       </c>
       <c r="BL9" s="3" t="n">
-        <v>0.444</v>
+        <v>0.468</v>
       </c>
       <c r="BM9" s="3" t="n">
-        <v>0.805</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="BN9" s="3" t="n">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="BO9" s="3" t="n">
-        <v>0.771</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="BP9" s="3" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="BQ9" s="3" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BR9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="BS9" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BT9" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BU9" s="3" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BV9" s="3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BW9" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BX9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="BY9" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BZ9" s="3" t="n">
-        <v>6.79</v>
+        <v>11.71</v>
       </c>
       <c r="CA9" s="3" t="n">
-        <v>0.218</v>
+        <v>0.316</v>
       </c>
       <c r="CB9" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="CC9" s="3" t="n">
-        <v>6.8</v>
+        <v>10.13</v>
       </c>
       <c r="CD9" s="3" t="n">
-        <v>1.484</v>
+        <v>2.603</v>
       </c>
       <c r="CE9" s="3" t="n">
-        <v>0.1875</v>
+        <v>0.2857</v>
       </c>
       <c r="CF9" s="3" t="n">
-        <v>0.1094</v>
+        <v>0.1429</v>
       </c>
       <c r="CG9" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.0794</v>
       </c>
       <c r="CH9" s="3" t="n">
-        <v>0.1094</v>
+        <v>0.0635</v>
       </c>
       <c r="CI9" s="3" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="CJ9" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CK9" s="3" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="CL9" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="CN9" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CO9" s="3" t="n">
-        <v>0.1952</v>
+        <v>0.1476</v>
       </c>
       <c r="CP9" s="3" t="n">
-        <v>0.073</v>
+        <v>0.0503</v>
       </c>
       <c r="CQ9" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.0029</v>
       </c>
       <c r="CR9" s="3" t="n">
-        <v>0.0457</v>
+        <v>0.0542</v>
       </c>
       <c r="CS9" s="3" t="n">
-        <v>0.1118</v>
+        <v>0.1169</v>
       </c>
       <c r="CT9" s="3" t="n">
-        <v>0.0198</v>
+        <v>0.0119</v>
       </c>
       <c r="CU9" s="3" t="n">
-        <v>0.131</v>
+        <v>0.1338</v>
       </c>
       <c r="CV9" s="3" t="n">
-        <v>0.1224</v>
+        <v>0.1398</v>
       </c>
       <c r="CW9" s="3" t="n">
-        <v>0.0077</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="CX9" s="4" t="inlineStr">
         <is>
@@ -3887,16 +3911,16 @@
         <v>10.37</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>68.3</v>
@@ -3904,38 +3928,38 @@
       <c r="P10" s="5" t="n">
         <v>68.3</v>
       </c>
-      <c r="Q10" s="5" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>54.8</v>
+      <c r="Q10" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>54.7</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
       <c r="X10" s="7" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
       <c r="Y10" s="7" t="n">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="Z10" s="7" t="n">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>260.06</v>
+        <v>260.07</v>
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
@@ -3944,7 +3968,7 @@
       </c>
       <c r="AC10" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.4 FS | Sim 9.7</t>
+          <t>Forecast 10.4 FS | Sim 9.8</t>
         </is>
       </c>
       <c r="AD10" s="3" t="n">
@@ -3952,10 +3976,12 @@
       </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF10" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG10" s="3" t="n">
         <v>2</v>
       </c>
@@ -4033,16 +4059,16 @@
         <v>1.03</v>
       </c>
       <c r="BC10" s="3" t="n">
-        <v>85.2</v>
+        <v>83.2</v>
       </c>
       <c r="BD10" s="3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BE10" s="3" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="BF10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG10" s="4" t="inlineStr">
         <is>
@@ -4139,7 +4165,7 @@
         <v>7</v>
       </c>
       <c r="CK10" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="CL10" s="3" t="n">
         <v>3</v>
@@ -4148,7 +4174,7 @@
         <v>15</v>
       </c>
       <c r="CN10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CO10" s="3" t="n">
         <v>0.1484</v>
@@ -4197,7 +4223,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4222,62 +4248,62 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>10.82</v>
+        <v>11.03</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.96</v>
+        <v>11.47</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>87.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>77.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>77.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>64.2</v>
+        <v>67.7</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="W11" s="7" t="n">
-        <v>51.6</v>
+        <v>67.7</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>55.2</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>51.6</v>
+        <v>55.2</v>
       </c>
       <c r="Y11" s="7" t="n">
-        <v>47.6</v>
+        <v>50.5</v>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>47.6</v>
+        <v>50.5</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>255.9</v>
+        <v>259.97</v>
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
@@ -4286,34 +4312,36 @@
       </c>
       <c r="AC11" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.8 FS | Sim 11.0</t>
+          <t>Forecast 11.0 FS | Sim 11.5</t>
         </is>
       </c>
       <c r="AD11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH11" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="AI11" s="4" t="inlineStr">
         <is>
-          <t>4-3-4-3-4</t>
+          <t>3-3-4-3</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="AL11" s="4" t="inlineStr">
         <is>
@@ -4321,7 +4349,7 @@
         </is>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN11" s="3" t="n">
         <v>1.04</v>
@@ -4384,46 +4412,46 @@
         </is>
       </c>
       <c r="BH11" s="3" t="n">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="BJ11" s="3" t="n">
-        <v>0.258</v>
+        <v>0.294</v>
       </c>
       <c r="BK11" s="3" t="n">
-        <v>0.327</v>
+        <v>0.361</v>
       </c>
       <c r="BL11" s="3" t="n">
-        <v>0.416</v>
+        <v>0.444</v>
       </c>
       <c r="BM11" s="3" t="n">
-        <v>0.743</v>
+        <v>0.805</v>
       </c>
       <c r="BN11" s="3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="BO11" s="3" t="n">
-        <v>0.739</v>
+        <v>0.771</v>
       </c>
       <c r="BP11" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="BQ11" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BR11" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS11" s="3" t="n">
         <v>9</v>
       </c>
       <c r="BT11" s="3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BU11" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BV11" s="3" t="n">
         <v>30</v>
@@ -4432,16 +4460,16 @@
         <v>6</v>
       </c>
       <c r="BX11" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BY11" s="3" t="n">
-        <v>6.14</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BZ11" s="3" t="n">
-        <v>8.07</v>
+        <v>6.79</v>
       </c>
       <c r="CA11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.218</v>
       </c>
       <c r="CB11" s="4" t="inlineStr">
         <is>
@@ -4449,31 +4477,31 @@
         </is>
       </c>
       <c r="CC11" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="CD11" s="3" t="n">
-        <v>2.018</v>
+        <v>1.484</v>
       </c>
       <c r="CE11" s="3" t="n">
-        <v>0.2143</v>
+        <v>0.1875</v>
       </c>
       <c r="CF11" s="3" t="n">
-        <v>0.1071</v>
+        <v>0.1094</v>
       </c>
       <c r="CG11" s="3" t="n">
-        <v>0.0357</v>
+        <v>0.0156</v>
       </c>
       <c r="CH11" s="3" t="n">
-        <v>0.1071</v>
+        <v>0.1094</v>
       </c>
       <c r="CI11" s="3" t="n">
-        <v>0.0357</v>
+        <v>0</v>
       </c>
       <c r="CJ11" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CK11" s="3" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
       <c r="CL11" s="3" t="n">
         <v>5</v>
@@ -4485,31 +4513,31 @@
         <v>23</v>
       </c>
       <c r="CO11" s="3" t="n">
-        <v>0.1794</v>
+        <v>0.1952</v>
       </c>
       <c r="CP11" s="3" t="n">
-        <v>0.0655</v>
+        <v>0.073</v>
       </c>
       <c r="CQ11" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="CR11" s="3" t="n">
-        <v>0.0483</v>
+        <v>0.0457</v>
       </c>
       <c r="CS11" s="3" t="n">
-        <v>0.1141</v>
+        <v>0.1118</v>
       </c>
       <c r="CT11" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.0198</v>
       </c>
       <c r="CU11" s="3" t="n">
-        <v>0.1231</v>
+        <v>0.131</v>
       </c>
       <c r="CV11" s="3" t="n">
-        <v>0.1337</v>
+        <v>0.1224</v>
       </c>
       <c r="CW11" s="3" t="n">
-        <v>0.0124</v>
+        <v>0.0077</v>
       </c>
       <c r="CX11" s="4" t="inlineStr">
         <is>
@@ -4531,22 +4559,22 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>MIL @ PIT</t>
+          <t>HOU @ TEX</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -4560,58 +4588,58 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>10.23</v>
+        <v>10.82</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="L12" s="5" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="O12" s="5" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="M12" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>65</v>
-      </c>
       <c r="P12" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="S12" s="7" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="T12" s="7" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="U12" s="7" t="n">
-        <v>46.5</v>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>57.3</v>
       </c>
       <c r="V12" s="7" t="n">
-        <v>46.5</v>
+        <v>57.3</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>42.9</v>
+        <v>51.8</v>
       </c>
       <c r="X12" s="7" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>39.9</v>
+        <v>51.8</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>47.6</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>255.22</v>
+        <v>256.34</v>
       </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
@@ -4620,7 +4648,7 @@
       </c>
       <c r="AC12" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.2 FS | Sim 9.5</t>
+          <t>Forecast 10.8 FS | Sim 11.0</t>
         </is>
       </c>
       <c r="AD12" s="3" t="n">
@@ -4628,10 +4656,12 @@
       </c>
       <c r="AE12" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF12" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AG12" s="3" t="n">
         <v>4</v>
       </c>
@@ -4640,14 +4670,14 @@
       </c>
       <c r="AI12" s="4" t="inlineStr">
         <is>
-          <t>4-4-4-4-4</t>
+          <t>4-3-4-3-4</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="AL12" s="4" t="inlineStr">
         <is>
@@ -4662,200 +4692,192 @@
       </c>
       <c r="AO12" s="4" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="AP12" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="n">
-        <v>4.15</v>
+        <v>10.22</v>
       </c>
       <c r="AR12" s="3" t="n">
-        <v>1.18</v>
+        <v>2.27</v>
       </c>
       <c r="AS12" s="3" t="n">
-        <v>0.2022</v>
+        <v>0.254</v>
       </c>
       <c r="AT12" s="3" t="n">
-        <v>0.0437</v>
+        <v>0.0476</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>0.0765</v>
+        <v>0.1905</v>
       </c>
       <c r="AV12" s="3" t="n">
-        <v>3.36</v>
+        <v>4.79</v>
       </c>
       <c r="AW12" s="3" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AX12" s="3" t="n">
-        <v>0.1939</v>
+        <v>0.2086</v>
       </c>
       <c r="AY12" s="3" t="n">
-        <v>0.0266</v>
+        <v>0.0365</v>
       </c>
       <c r="AZ12" s="4" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BA12" s="3" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="BB12" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC12" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="BD12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE12" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF12" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="BC12" s="4" t="n"/>
+      <c r="BD12" s="4" t="n"/>
+      <c r="BE12" s="4" t="n"/>
+      <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="BH12" s="3" t="n">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>90</v>
+        <v>341</v>
       </c>
       <c r="BJ12" s="3" t="n">
-        <v>0.311</v>
+        <v>0.258</v>
       </c>
       <c r="BK12" s="3" t="n">
-        <v>0.37</v>
+        <v>0.327</v>
       </c>
       <c r="BL12" s="3" t="n">
-        <v>0.722</v>
+        <v>0.416</v>
       </c>
       <c r="BM12" s="3" t="n">
-        <v>1.092</v>
+        <v>0.743</v>
       </c>
       <c r="BN12" s="3" t="n">
-        <v>31</v>
+        <v>286</v>
       </c>
       <c r="BO12" s="3" t="n">
-        <v>1.387</v>
+        <v>0.739</v>
       </c>
       <c r="BP12" s="3" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="BQ12" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT12" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BU12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BV12" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BY12" s="3" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BZ12" s="3" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="CA12" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="CB12" s="4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="CC12" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CD12" s="3" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="CE12" s="3" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="CF12" s="3" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="CG12" s="3" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="CH12" s="3" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="CI12" s="3" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="CJ12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CK12" s="3" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="CL12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="BR12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT12" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BU12" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BV12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BW12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" s="3" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="BZ12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA12" s="3" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="CB12" s="4" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="CC12" s="3" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="CD12" s="3" t="n">
-        <v>3.328</v>
-      </c>
-      <c r="CE12" s="3" t="n">
-        <v>0.3443</v>
-      </c>
-      <c r="CF12" s="3" t="n">
-        <v>0.1803</v>
-      </c>
-      <c r="CG12" s="3" t="n">
-        <v>0.1148</v>
-      </c>
-      <c r="CH12" s="3" t="n">
-        <v>0.1148</v>
-      </c>
-      <c r="CI12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="CK12" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="CL12" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="CM12" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CN12" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CO12" s="3" t="n">
-        <v>0.1212</v>
+        <v>0.1794</v>
       </c>
       <c r="CP12" s="3" t="n">
-        <v>0.0407</v>
+        <v>0.0655</v>
       </c>
       <c r="CQ12" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="CR12" s="3" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="CS12" s="3" t="n">
-        <v>0.083</v>
+        <v>0.1141</v>
       </c>
       <c r="CT12" s="3" t="n">
-        <v>0.0083</v>
+        <v>0.0155</v>
       </c>
       <c r="CU12" s="3" t="n">
-        <v>0.146</v>
+        <v>0.1231</v>
       </c>
       <c r="CV12" s="3" t="n">
-        <v>0.1965</v>
+        <v>0.1337</v>
       </c>
       <c r="CW12" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.0124</v>
       </c>
       <c r="CX12" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4873,22 +4895,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>ATL @ STL</t>
+          <t>MIL @ PIT</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -4902,58 +4924,58 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>80.3</v>
+        <v>76.5</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>73.2</v>
+        <v>68.7</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>73.2</v>
+        <v>68.7</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>68.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>55</v>
+        <v>64.40000000000001</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>51.3</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>55</v>
+        <v>51.3</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>48.2</v>
+        <v>45.3</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>48.2</v>
+        <v>45.3</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>44.2</v>
+        <v>42</v>
       </c>
       <c r="X13" s="7" t="n">
-        <v>44.2</v>
+        <v>42</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>39.8</v>
+        <v>38.9</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>39.8</v>
+        <v>38.9</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>253.6</v>
+        <v>253.83</v>
       </c>
       <c r="AB13" s="4" t="inlineStr">
         <is>
@@ -4962,34 +4984,36 @@
       </c>
       <c r="AC13" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.5 FS | Sim 9.6</t>
+          <t>Forecast 10.2 FS | Sim 9.4</t>
         </is>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF13" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AG13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI13" s="4" t="inlineStr">
         <is>
-          <t>4-3-4-3-3-4-3</t>
+          <t>4-4-4-4-4</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>4.92</v>
+        <v>4.73</v>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
@@ -4997,135 +5021,135 @@
         </is>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN13" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>JR Ritchie</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="AP13" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AR13" s="3" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AS13" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2022</v>
       </c>
       <c r="AT13" s="3" t="n">
-        <v>0.035</v>
+        <v>0.0437</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>0.14</v>
+        <v>0.0765</v>
       </c>
       <c r="AV13" s="3" t="n">
-        <v>3.61</v>
+        <v>3.36</v>
       </c>
       <c r="AW13" s="3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AX13" s="3" t="n">
-        <v>0.2043</v>
+        <v>0.1939</v>
       </c>
       <c r="AY13" s="3" t="n">
-        <v>0.0305</v>
+        <v>0.0266</v>
       </c>
       <c r="AZ13" s="4" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BA13" s="3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="BB13" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="BC13" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="BD13" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE13" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="BD13" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE13" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="BF13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG13" s="4" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BH13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI13" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ13" s="3" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BK13" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BL13" s="3" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="BM13" s="3" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="BN13" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="BO13" s="3" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="BP13" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT13" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU13" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BV13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BW13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="BH13" s="3" t="n">
-        <v>391</v>
-      </c>
-      <c r="BI13" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="BJ13" s="3" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="BK13" s="3" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="BL13" s="3" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="BM13" s="3" t="n">
-        <v>0.887</v>
-      </c>
-      <c r="BN13" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="BO13" s="3" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="BP13" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="BQ13" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BR13" s="3" t="n">
+      <c r="BX13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="BS13" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU13" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="BV13" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="BW13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX13" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="BY13" s="3" t="n">
-        <v>10.71</v>
+        <v>12.43</v>
       </c>
       <c r="BZ13" s="3" t="n">
-        <v>11.93</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" s="3" t="n">
-        <v>0.319</v>
+        <v>0.396</v>
       </c>
       <c r="CB13" s="4" t="inlineStr">
         <is>
@@ -5133,67 +5157,67 @@
         </is>
       </c>
       <c r="CC13" s="3" t="n">
-        <v>8.77</v>
+        <v>10.26</v>
       </c>
       <c r="CD13" s="3" t="n">
-        <v>2.93</v>
+        <v>3.328</v>
       </c>
       <c r="CE13" s="3" t="n">
-        <v>0.2632</v>
+        <v>0.3443</v>
       </c>
       <c r="CF13" s="3" t="n">
-        <v>0.1228</v>
+        <v>0.1803</v>
       </c>
       <c r="CG13" s="3" t="n">
-        <v>0.0702</v>
+        <v>0.1148</v>
       </c>
       <c r="CH13" s="3" t="n">
-        <v>0.1404</v>
+        <v>0.1148</v>
       </c>
       <c r="CI13" s="3" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="CJ13" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK13" s="3" t="n">
-        <v>8.32</v>
+        <v>8.68</v>
       </c>
       <c r="CL13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="CM13" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CN13" s="3" t="n">
         <v>21</v>
       </c>
       <c r="CO13" s="3" t="n">
-        <v>0.1349</v>
+        <v>0.1212</v>
       </c>
       <c r="CP13" s="3" t="n">
-        <v>0.0424</v>
+        <v>0.0407</v>
       </c>
       <c r="CQ13" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.0048</v>
       </c>
       <c r="CR13" s="3" t="n">
-        <v>0.0513</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="CS13" s="3" t="n">
-        <v>0.1145</v>
+        <v>0.083</v>
       </c>
       <c r="CT13" s="3" t="n">
-        <v>0.014</v>
+        <v>0.0083</v>
       </c>
       <c r="CU13" s="3" t="n">
-        <v>0.137</v>
+        <v>0.146</v>
       </c>
       <c r="CV13" s="3" t="n">
-        <v>0.1844</v>
+        <v>0.1965</v>
       </c>
       <c r="CW13" s="3" t="n">
-        <v>0.0174</v>
+        <v>0.0101</v>
       </c>
       <c r="CX13" s="4" t="inlineStr">
         <is>
@@ -5215,87 +5239,87 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>CHC @ CIN</t>
+          <t>HOU @ TEX</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>10.22</v>
+        <v>10.79</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>9.98</v>
+        <v>10.87</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>82</v>
+        <v>85.3</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>75</v>
+        <v>77.7</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75</v>
+        <v>77.7</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>70.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>70.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>60.5</v>
+        <v>65</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="T14" s="7" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U14" s="7" t="n">
-        <v>50.3</v>
+        <v>65</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>54.4</v>
       </c>
       <c r="V14" s="7" t="n">
-        <v>50.3</v>
+        <v>54.4</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>45.7</v>
+        <v>49.6</v>
       </c>
       <c r="X14" s="7" t="n">
-        <v>45.7</v>
+        <v>49.6</v>
       </c>
       <c r="Y14" s="7" t="n">
-        <v>42</v>
+        <v>46.1</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>42</v>
+        <v>46.1</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>253.56</v>
+        <v>252.17</v>
       </c>
       <c r="AB14" s="4" t="inlineStr">
         <is>
@@ -5304,34 +5328,36 @@
       </c>
       <c r="AC14" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.2 FS | Sim 10.0</t>
+          <t>Forecast 10.8 FS | Sim 10.9</t>
         </is>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AG14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI14" s="4" t="inlineStr">
         <is>
-          <t>2-4-4-4-3-4</t>
+          <t>5-5-3-3-2</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="AL14" s="4" t="inlineStr">
         <is>
@@ -5346,95 +5372,87 @@
       </c>
       <c r="AO14" s="4" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="AP14" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="n">
-        <v>3.92</v>
+        <v>10.22</v>
       </c>
       <c r="AR14" s="3" t="n">
-        <v>1.41</v>
+        <v>2.27</v>
       </c>
       <c r="AS14" s="3" t="n">
-        <v>0.2215</v>
+        <v>0.254</v>
       </c>
       <c r="AT14" s="3" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AV14" s="3" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AW14" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX14" s="3" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="AY14" s="3" t="n">
         <v>0.0365</v>
       </c>
-      <c r="AU14" s="3" t="n">
-        <v>0.1027</v>
-      </c>
-      <c r="AV14" s="3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="AW14" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX14" s="3" t="n">
-        <v>0.2126</v>
-      </c>
-      <c r="AY14" s="3" t="n">
-        <v>0.0341</v>
-      </c>
       <c r="AZ14" s="4" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BA14" s="3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BB14" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="BD14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE14" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="BF14" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BC14" s="4" t="n"/>
+      <c r="BD14" s="4" t="n"/>
+      <c r="BE14" s="4" t="n"/>
+      <c r="BF14" s="4" t="n"/>
       <c r="BG14" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="BH14" s="3" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="BJ14" s="3" t="n">
-        <v>0.269</v>
+        <v>0.242</v>
       </c>
       <c r="BK14" s="3" t="n">
-        <v>0.349</v>
+        <v>0.304</v>
       </c>
       <c r="BL14" s="3" t="n">
-        <v>0.468</v>
+        <v>0.427</v>
       </c>
       <c r="BM14" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="BN14" s="3" t="n">
-        <v>93</v>
+        <v>289</v>
       </c>
       <c r="BO14" s="3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BP14" s="3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BQ14" s="3" t="n">
         <v>14</v>
@@ -5443,103 +5461,103 @@
         <v>0</v>
       </c>
       <c r="BS14" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BT14" s="3" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BU14" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="BV14" s="3" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="BW14" s="3" t="n">
         <v>3</v>
       </c>
       <c r="BX14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY14" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="BZ14" s="3" t="n">
-        <v>11.71</v>
+        <v>7.29</v>
       </c>
       <c r="CA14" s="3" t="n">
-        <v>0.316</v>
+        <v>0.189</v>
       </c>
       <c r="CB14" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="CC14" s="3" t="n">
-        <v>10.13</v>
+        <v>7.57</v>
       </c>
       <c r="CD14" s="3" t="n">
-        <v>2.603</v>
+        <v>1.759</v>
       </c>
       <c r="CE14" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.1724</v>
       </c>
       <c r="CF14" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.0517</v>
       </c>
       <c r="CG14" s="3" t="n">
-        <v>0.0794</v>
+        <v>0.0517</v>
       </c>
       <c r="CH14" s="3" t="n">
-        <v>0.0635</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="CI14" s="3" t="n">
-        <v>0.0159</v>
+        <v>0.0172</v>
       </c>
       <c r="CJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="CK14" s="3" t="n">
-        <v>8.34</v>
+        <v>8.75</v>
       </c>
       <c r="CL14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM14" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CN14" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CO14" s="3" t="n">
-        <v>0.1476</v>
+        <v>0.1788</v>
       </c>
       <c r="CP14" s="3" t="n">
-        <v>0.0503</v>
+        <v>0.0487</v>
       </c>
       <c r="CQ14" s="3" t="n">
-        <v>0.0029</v>
+        <v>0.0033</v>
       </c>
       <c r="CR14" s="3" t="n">
-        <v>0.0542</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="CS14" s="3" t="n">
-        <v>0.1169</v>
+        <v>0.1075</v>
       </c>
       <c r="CT14" s="3" t="n">
-        <v>0.0119</v>
+        <v>0.0141</v>
       </c>
       <c r="CU14" s="3" t="n">
-        <v>0.1279</v>
+        <v>0.1155</v>
       </c>
       <c r="CV14" s="3" t="n">
-        <v>0.1684</v>
+        <v>0.1785</v>
       </c>
       <c r="CW14" s="3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="CX14" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5557,22 +5575,22 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>HOU @ TEX</t>
+          <t>COL @ SF</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -5582,62 +5600,62 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>10.79</v>
+        <v>10.61</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10.64</v>
+        <v>10.56</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>85.2</v>
+        <v>86.5</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>59.8</v>
+        <v>60.6</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>59.8</v>
+        <v>60.6</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>53.2</v>
+        <v>55.4</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>53.2</v>
+        <v>55.4</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>44.8</v>
+        <v>46.3</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>44.8</v>
+        <v>46.3</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>250.17</v>
+        <v>249.55</v>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
@@ -5646,34 +5664,36 @@
       </c>
       <c r="AC15" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.8 FS | Sim 10.6</t>
+          <t>Forecast 10.6 FS | Sim 10.6</t>
         </is>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AG15" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI15" s="4" t="inlineStr">
         <is>
-          <t>5-5-3-3-2</t>
+          <t>3-3-3-3-3-3-2</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>40</v>
+        <v>85.7</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>4.61</v>
+        <v>4.92</v>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
@@ -5681,14 +5701,14 @@
         </is>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN15" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="AP15" s="4" t="inlineStr">
@@ -5697,143 +5717,151 @@
         </is>
       </c>
       <c r="AQ15" s="3" t="n">
-        <v>10.22</v>
+        <v>6.46</v>
       </c>
       <c r="AR15" s="3" t="n">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="AS15" s="3" t="n">
-        <v>0.254</v>
+        <v>0.2925</v>
       </c>
       <c r="AT15" s="3" t="n">
-        <v>0.0476</v>
+        <v>0.0317</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.0794</v>
       </c>
       <c r="AV15" s="3" t="n">
-        <v>4.79</v>
+        <v>5.46</v>
       </c>
       <c r="AW15" s="3" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AX15" s="3" t="n">
-        <v>0.2086</v>
+        <v>0.2552</v>
       </c>
       <c r="AY15" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0346</v>
       </c>
       <c r="AZ15" s="4" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BA15" s="3" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BB15" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD15" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BE15" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="BF15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" s="4" t="inlineStr">
+        <is>
+          <t>light wind</t>
+        </is>
+      </c>
+      <c r="BH15" s="3" t="n">
+        <v>366</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>346</v>
+      </c>
+      <c r="BJ15" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BK15" s="3" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BL15" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM15" s="3" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="BN15" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="BO15" s="3" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BP15" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="BQ15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BR15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="inlineStr">
-        <is>
-          <t>Indoor/retractable neutral</t>
-        </is>
-      </c>
-      <c r="BH15" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="BI15" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="BJ15" s="3" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="BK15" s="3" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="BL15" s="3" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="BM15" s="3" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="BN15" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="BO15" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BP15" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="BQ15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR15" s="3" t="n">
+      <c r="BS15" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT15" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BU15" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BV15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BW15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BY15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ15" s="3" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="CA15" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="CB15" s="4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="CC15" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CD15" s="3" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="CE15" s="3" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="CF15" s="3" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="CG15" s="3" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="CH15" s="3" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="CI15" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="BS15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BT15" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="BU15" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="BV15" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY15" s="3" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="BZ15" s="3" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="CA15" s="3" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="CB15" s="4" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="CC15" s="3" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="CD15" s="3" t="n">
-        <v>1.759</v>
-      </c>
-      <c r="CE15" s="3" t="n">
-        <v>0.1724</v>
-      </c>
-      <c r="CF15" s="3" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="CG15" s="3" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="CH15" s="3" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="CI15" s="3" t="n">
-        <v>0.0172</v>
       </c>
       <c r="CJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="CK15" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="CL15" s="3" t="n">
         <v>4</v>
@@ -5842,34 +5870,34 @@
         <v>16</v>
       </c>
       <c r="CN15" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CO15" s="3" t="n">
-        <v>0.1788</v>
+        <v>0.2096</v>
       </c>
       <c r="CP15" s="3" t="n">
-        <v>0.0487</v>
+        <v>0.0582</v>
       </c>
       <c r="CQ15" s="3" t="n">
-        <v>0.0033</v>
+        <v>0.0045</v>
       </c>
       <c r="CR15" s="3" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0477</v>
       </c>
       <c r="CS15" s="3" t="n">
-        <v>0.1075</v>
+        <v>0.05</v>
       </c>
       <c r="CT15" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.0138</v>
       </c>
       <c r="CU15" s="3" t="n">
-        <v>0.1155</v>
+        <v>0.1193</v>
       </c>
       <c r="CV15" s="3" t="n">
-        <v>0.1785</v>
+        <v>0.1479</v>
       </c>
       <c r="CW15" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.0125</v>
       </c>
       <c r="CX15" s="4" t="inlineStr">
         <is>
@@ -5923,46 +5951,46 @@
         <v>10.1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>9.81</v>
+        <v>9.75</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>80.8</v>
+        <v>81.3</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>54.7</v>
+        <v>55.2</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>54.7</v>
+        <v>55.2</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="X16" s="7" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="Y16" s="7" t="n">
         <v>40.1</v>
@@ -5971,7 +5999,7 @@
         <v>40.1</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>249.84</v>
+        <v>249.55</v>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
@@ -5988,10 +6016,12 @@
       </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF16" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG16" s="3" t="n">
         <v>2</v>
       </c>
@@ -6167,7 +6197,7 @@
         <v>7</v>
       </c>
       <c r="CK16" s="3" t="n">
-        <v>8.57</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="CL16" s="3" t="n">
         <v>3</v>
@@ -6176,7 +6206,7 @@
         <v>15</v>
       </c>
       <c r="CN16" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CO16" s="3" t="n">
         <v>0.1419</v>
@@ -6225,87 +6255,87 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>COL @ SF</t>
+          <t>TOR @ SD</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>10.61</v>
+        <v>10.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.49</v>
+        <v>10.13</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>86.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>76.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>76.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>74.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>74.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>65</v>
+        <v>59.2</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>55.2</v>
+        <v>59.2</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="T17" s="7" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>49.6</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>55.2</v>
+        <v>49.6</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>48.8</v>
+        <v>45.9</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>48.8</v>
+        <v>45.9</v>
       </c>
       <c r="Y17" s="7" t="n">
-        <v>45.8</v>
+        <v>42.4</v>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>45.8</v>
+        <v>42.4</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>248.98</v>
+        <v>249.26</v>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
@@ -6314,7 +6344,7 @@
       </c>
       <c r="AC17" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.6 FS | Sim 10.5</t>
+          <t>Forecast 10.4 FS | Sim 10.1</t>
         </is>
       </c>
       <c r="AD17" s="3" t="n">
@@ -6334,11 +6364,11 @@
       </c>
       <c r="AI17" s="4" t="inlineStr">
         <is>
-          <t>3-3-3-3-3-3-2</t>
+          <t>5-3-6-4-4-3-3</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="n">
-        <v>85.7</v>
+        <v>42.9</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>4.92</v>
@@ -6349,14 +6379,14 @@
         </is>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN17" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO17" s="4" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Germán Márquez</t>
         </is>
       </c>
       <c r="AP17" s="4" t="inlineStr">
@@ -6365,119 +6395,119 @@
         </is>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>6.46</v>
+        <v>5.02</v>
       </c>
       <c r="AR17" s="3" t="n">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="AS17" s="3" t="n">
-        <v>0.2925</v>
+        <v>0.2236</v>
       </c>
       <c r="AT17" s="3" t="n">
-        <v>0.0317</v>
+        <v>0.0497</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>0.0794</v>
+        <v>0.1118</v>
       </c>
       <c r="AV17" s="3" t="n">
-        <v>5.46</v>
+        <v>4.23</v>
       </c>
       <c r="AW17" s="3" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AX17" s="3" t="n">
-        <v>0.2552</v>
+        <v>0.2187</v>
       </c>
       <c r="AY17" s="3" t="n">
-        <v>0.0346</v>
+        <v>0.0291</v>
       </c>
       <c r="AZ17" s="4" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BA17" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BB17" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="BC17" s="3" t="n">
-        <v>72.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BD17" s="3" t="n">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="BF17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t>light wind</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="BH17" s="3" t="n">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="BJ17" s="3" t="n">
-        <v>0.28</v>
+        <v>0.235</v>
       </c>
       <c r="BK17" s="3" t="n">
-        <v>0.309</v>
+        <v>0.315</v>
       </c>
       <c r="BL17" s="3" t="n">
-        <v>0.5</v>
+        <v>0.464</v>
       </c>
       <c r="BM17" s="3" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="BN17" s="3" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="BO17" s="3" t="n">
-        <v>0.791</v>
+        <v>0.778</v>
       </c>
       <c r="BP17" s="3" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="BQ17" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BR17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS17" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BT17" s="3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BU17" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="BV17" s="3" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="BW17" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BX17" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BY17" s="3" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BZ17" s="3" t="n">
-        <v>6.79</v>
+        <v>8.93</v>
       </c>
       <c r="CA17" s="3" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="CB17" s="4" t="inlineStr">
         <is>
@@ -6485,34 +6515,34 @@
         </is>
       </c>
       <c r="CC17" s="3" t="n">
-        <v>6.6</v>
+        <v>8.93</v>
       </c>
       <c r="CD17" s="3" t="n">
-        <v>1.667</v>
+        <v>2.155</v>
       </c>
       <c r="CE17" s="3" t="n">
-        <v>0.2105</v>
+        <v>0.2069</v>
       </c>
       <c r="CF17" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.0862</v>
       </c>
       <c r="CG17" s="3" t="n">
-        <v>0.0526</v>
+        <v>0.0862</v>
       </c>
       <c r="CH17" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.0517</v>
       </c>
       <c r="CI17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CJ17" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK17" s="3" t="n">
-        <v>8.359999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="CL17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM17" s="3" t="n">
         <v>16</v>
@@ -6521,35 +6551,35 @@
         <v>22</v>
       </c>
       <c r="CO17" s="3" t="n">
-        <v>0.2096</v>
+        <v>0.1342</v>
       </c>
       <c r="CP17" s="3" t="n">
-        <v>0.0582</v>
+        <v>0.0333</v>
       </c>
       <c r="CQ17" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.0024</v>
       </c>
       <c r="CR17" s="3" t="n">
-        <v>0.0477</v>
+        <v>0.0653</v>
       </c>
       <c r="CS17" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1064</v>
       </c>
       <c r="CT17" s="3" t="n">
-        <v>0.0138</v>
+        <v>0.0153</v>
       </c>
       <c r="CU17" s="3" t="n">
-        <v>0.1193</v>
+        <v>0.1274</v>
       </c>
       <c r="CV17" s="3" t="n">
-        <v>0.1479</v>
+        <v>0.1698</v>
       </c>
       <c r="CW17" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.0071</v>
       </c>
       <c r="CX17" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6567,27 +6597,27 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>KC @ BAL</t>
+          <t>NYY @ WSH</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -6596,58 +6626,58 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>10.25</v>
+        <v>10.07</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.04</v>
+        <v>9.76</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>83.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>75.5</v>
+        <v>73.5</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>75.5</v>
+        <v>73.5</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>71.5</v>
+        <v>69</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>71.5</v>
+        <v>69</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>61.4</v>
+        <v>59.1</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>61.4</v>
+        <v>59.1</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="T18" s="7" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>50.4</v>
+        <v>48.4</v>
       </c>
       <c r="V18" s="7" t="n">
-        <v>50.4</v>
+        <v>48.4</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>45.7</v>
+        <v>44.2</v>
       </c>
       <c r="X18" s="7" t="n">
-        <v>45.7</v>
+        <v>44.2</v>
       </c>
       <c r="Y18" s="7" t="n">
-        <v>41.8</v>
+        <v>40.6</v>
       </c>
       <c r="Z18" s="7" t="n">
-        <v>41.8</v>
+        <v>40.6</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>248.79</v>
+        <v>248.8</v>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
@@ -6656,34 +6686,36 @@
       </c>
       <c r="AC18" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.2 FS | Sim 10.0</t>
+          <t>Forecast 10.1 FS | Sim 9.8</t>
         </is>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF18" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG18" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH18" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" s="4" t="inlineStr">
         <is>
-          <t>4-4-4-4-4-4-4</t>
+          <t>2-2-2-3-2-2</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>4.82</v>
+        <v>5.02</v>
       </c>
       <c r="AL18" s="4" t="inlineStr">
         <is>
@@ -6698,7 +6730,7 @@
       </c>
       <c r="AO18" s="4" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="AP18" s="4" t="inlineStr">
@@ -6707,54 +6739,54 @@
         </is>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>4.56</v>
+        <v>3.88</v>
       </c>
       <c r="AR18" s="3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AS18" s="3" t="n">
-        <v>0.2599</v>
+        <v>0.2354</v>
       </c>
       <c r="AT18" s="3" t="n">
-        <v>0.0325</v>
+        <v>0.0194</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>0.0742</v>
+        <v>0.0752</v>
       </c>
       <c r="AV18" s="3" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="AW18" s="3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AX18" s="3" t="n">
-        <v>0.2326</v>
+        <v>0.2294</v>
       </c>
       <c r="AY18" s="3" t="n">
-        <v>0.0346</v>
+        <v>0.0363</v>
       </c>
       <c r="AZ18" s="4" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BA18" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="BB18" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="BC18" s="3" t="n">
-        <v>85.2</v>
+        <v>83.2</v>
       </c>
       <c r="BD18" s="3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BE18" s="3" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="BF18" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BG18" s="4" t="inlineStr">
         <is>
@@ -6762,64 +6794,64 @@
         </is>
       </c>
       <c r="BH18" s="3" t="n">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="BJ18" s="3" t="n">
-        <v>0.253</v>
+        <v>0.279</v>
       </c>
       <c r="BK18" s="3" t="n">
-        <v>0.348</v>
+        <v>0.373</v>
       </c>
       <c r="BL18" s="3" t="n">
-        <v>0.478</v>
+        <v>0.598</v>
       </c>
       <c r="BM18" s="3" t="n">
-        <v>0.826</v>
+        <v>0.971</v>
       </c>
       <c r="BN18" s="3" t="n">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="BO18" s="3" t="n">
-        <v>0.887</v>
+        <v>1.055</v>
       </c>
       <c r="BP18" s="3" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="BQ18" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BR18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS18" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BT18" s="3" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="BU18" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BV18" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW18" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BX18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="BY18" s="3" t="n">
-        <v>10.86</v>
+        <v>15.43</v>
       </c>
       <c r="BZ18" s="3" t="n">
-        <v>8.5</v>
+        <v>10.79</v>
       </c>
       <c r="CA18" s="3" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="CB18" s="4" t="inlineStr">
         <is>
@@ -6827,67 +6859,67 @@
         </is>
       </c>
       <c r="CC18" s="3" t="n">
-        <v>9.630000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="CD18" s="3" t="n">
-        <v>2.017</v>
+        <v>2.517</v>
       </c>
       <c r="CE18" s="3" t="n">
-        <v>0.2034</v>
+        <v>0.2333</v>
       </c>
       <c r="CF18" s="3" t="n">
-        <v>0.1017</v>
+        <v>0.1167</v>
       </c>
       <c r="CG18" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.1167</v>
       </c>
       <c r="CH18" s="3" t="n">
-        <v>0.1695</v>
+        <v>0.1333</v>
       </c>
       <c r="CI18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CJ18" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK18" s="3" t="n">
-        <v>8.33</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="CL18" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="CN18" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CO18" s="3" t="n">
-        <v>0.1518</v>
+        <v>0.137</v>
       </c>
       <c r="CP18" s="3" t="n">
-        <v>0.053</v>
+        <v>0.0419</v>
       </c>
       <c r="CQ18" s="3" t="n">
-        <v>0.0029</v>
+        <v>0.0042</v>
       </c>
       <c r="CR18" s="3" t="n">
-        <v>0.051</v>
+        <v>0.0516</v>
       </c>
       <c r="CS18" s="3" t="n">
-        <v>0.1113</v>
+        <v>0.1048</v>
       </c>
       <c r="CT18" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="CU18" s="3" t="n">
-        <v>0.1243</v>
+        <v>0.1335</v>
       </c>
       <c r="CV18" s="3" t="n">
-        <v>0.1709</v>
+        <v>0.1496</v>
       </c>
       <c r="CW18" s="3" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="CX18" s="4" t="inlineStr">
         <is>
@@ -6909,87 +6941,87 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>TOR @ SD</t>
+          <t>KC @ BAL</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>10.4</v>
+        <v>10.18</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10.09</v>
+        <v>9.93</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>72.7</v>
+        <v>75.8</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>72.7</v>
+        <v>75.8</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>67.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>67.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>58.3</v>
+        <v>61</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>58.3</v>
+        <v>61</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>54.6</v>
+        <v>57</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>54.6</v>
+        <v>57</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>44.7</v>
+        <v>45.8</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>44.7</v>
+        <v>45.8</v>
       </c>
       <c r="Y19" s="7" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="Z19" s="7" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>248.64</v>
+        <v>247.41</v>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
@@ -6998,34 +7030,36 @@
       </c>
       <c r="AC19" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.4 FS | Sim 10.1</t>
+          <t>Forecast 10.2 FS | Sim 9.9</t>
         </is>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE19" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF19" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AG19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AI19" s="4" t="inlineStr">
         <is>
-          <t>5-3-6-4-4-3-3</t>
+          <t>4-4-4-4-4-4-4</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
@@ -7040,7 +7074,7 @@
       </c>
       <c r="AO19" s="4" t="inlineStr">
         <is>
-          <t>Germán Márquez</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="AP19" s="4" t="inlineStr">
@@ -7049,119 +7083,119 @@
         </is>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>5.02</v>
+        <v>4.56</v>
       </c>
       <c r="AR19" s="3" t="n">
         <v>1.43</v>
       </c>
       <c r="AS19" s="3" t="n">
-        <v>0.2236</v>
+        <v>0.2599</v>
       </c>
       <c r="AT19" s="3" t="n">
-        <v>0.0497</v>
+        <v>0.0325</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>0.1118</v>
+        <v>0.0742</v>
       </c>
       <c r="AV19" s="3" t="n">
-        <v>4.23</v>
+        <v>4.91</v>
       </c>
       <c r="AW19" s="3" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AX19" s="3" t="n">
-        <v>0.2187</v>
+        <v>0.2326</v>
       </c>
       <c r="AY19" s="3" t="n">
-        <v>0.0291</v>
+        <v>0.0346</v>
       </c>
       <c r="AZ19" s="4" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BA19" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" s="3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="BD19" s="3" t="n">
-        <v>8.1</v>
+        <v>2.9</v>
       </c>
       <c r="BE19" s="3" t="n">
-        <v>264</v>
+        <v>141</v>
       </c>
       <c r="BF19" s="3" t="n">
         <v>2</v>
       </c>
       <c r="BG19" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>humid</t>
         </is>
       </c>
       <c r="BH19" s="3" t="n">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="BJ19" s="3" t="n">
-        <v>0.235</v>
+        <v>0.253</v>
       </c>
       <c r="BK19" s="3" t="n">
-        <v>0.315</v>
+        <v>0.348</v>
       </c>
       <c r="BL19" s="3" t="n">
-        <v>0.464</v>
+        <v>0.478</v>
       </c>
       <c r="BM19" s="3" t="n">
-        <v>0.779</v>
+        <v>0.826</v>
       </c>
       <c r="BN19" s="3" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="BO19" s="3" t="n">
-        <v>0.778</v>
+        <v>0.887</v>
       </c>
       <c r="BP19" s="3" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="BQ19" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BR19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="BS19" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT19" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="BU19" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="BV19" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="BU19" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="BV19" s="3" t="n">
-        <v>35</v>
-      </c>
       <c r="BW19" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BX19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BY19" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="BZ19" s="3" t="n">
-        <v>8.93</v>
+        <v>8.5</v>
       </c>
       <c r="CA19" s="3" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="CB19" s="4" t="inlineStr">
         <is>
@@ -7169,67 +7203,67 @@
         </is>
       </c>
       <c r="CC19" s="3" t="n">
-        <v>8.93</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="CD19" s="3" t="n">
-        <v>2.155</v>
+        <v>2.017</v>
       </c>
       <c r="CE19" s="3" t="n">
-        <v>0.2069</v>
+        <v>0.2034</v>
       </c>
       <c r="CF19" s="3" t="n">
-        <v>0.0862</v>
+        <v>0.1017</v>
       </c>
       <c r="CG19" s="3" t="n">
-        <v>0.0862</v>
+        <v>0.0508</v>
       </c>
       <c r="CH19" s="3" t="n">
-        <v>0.0517</v>
+        <v>0.1695</v>
       </c>
       <c r="CI19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CJ19" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CK19" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="CL19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM19" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CN19" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CO19" s="3" t="n">
-        <v>0.1342</v>
+        <v>0.1518</v>
       </c>
       <c r="CP19" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.0519</v>
       </c>
       <c r="CQ19" s="3" t="n">
-        <v>0.0024</v>
+        <v>0.0029</v>
       </c>
       <c r="CR19" s="3" t="n">
-        <v>0.0653</v>
+        <v>0.05</v>
       </c>
       <c r="CS19" s="3" t="n">
-        <v>0.1064</v>
+        <v>0.1113</v>
       </c>
       <c r="CT19" s="3" t="n">
-        <v>0.0153</v>
+        <v>0.0111</v>
       </c>
       <c r="CU19" s="3" t="n">
-        <v>0.1274</v>
+        <v>0.1243</v>
       </c>
       <c r="CV19" s="3" t="n">
-        <v>0.1698</v>
+        <v>0.1709</v>
       </c>
       <c r="CW19" s="3" t="n">
-        <v>0.0071</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="CX19" s="4" t="inlineStr">
         <is>
@@ -7251,87 +7285,87 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>NYY @ WSH</t>
+          <t>CHC @ CIN</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
         <v>10.07</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>80.5</v>
+        <v>82.3</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>58.5</v>
+        <v>60.5</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>58.5</v>
+        <v>60.5</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>54.7</v>
+        <v>57.1</v>
       </c>
       <c r="T20" s="7" t="n">
-        <v>54.7</v>
+        <v>57.1</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>47.6</v>
+        <v>50.1</v>
       </c>
       <c r="V20" s="7" t="n">
-        <v>47.6</v>
+        <v>50.1</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>43.4</v>
+        <v>45.4</v>
       </c>
       <c r="X20" s="7" t="n">
-        <v>43.4</v>
+        <v>45.4</v>
       </c>
       <c r="Y20" s="7" t="n">
-        <v>40.1</v>
+        <v>42</v>
       </c>
       <c r="Z20" s="7" t="n">
-        <v>40.1</v>
+        <v>42</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>247.75</v>
+        <v>245.3</v>
       </c>
       <c r="AB20" s="4" t="inlineStr">
         <is>
@@ -7340,34 +7374,36 @@
       </c>
       <c r="AC20" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.1 FS | Sim 9.7</t>
+          <t>Forecast 10.1 FS | Sim 9.9</t>
         </is>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF20" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20" s="4" t="inlineStr">
         <is>
-          <t>2-2-2-3-2-2</t>
+          <t>1-1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
       <c r="AL20" s="4" t="inlineStr">
         <is>
@@ -7382,63 +7418,63 @@
       </c>
       <c r="AO20" s="4" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="AP20" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="n">
-        <v>3.88</v>
+        <v>4.31</v>
       </c>
       <c r="AR20" s="3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AS20" s="3" t="n">
-        <v>0.2354</v>
+        <v>0.2381</v>
       </c>
       <c r="AT20" s="3" t="n">
-        <v>0.0194</v>
+        <v>0.0238</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>0.0752</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AV20" s="3" t="n">
-        <v>4.75</v>
+        <v>4.34</v>
       </c>
       <c r="AW20" s="3" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AX20" s="3" t="n">
-        <v>0.2294</v>
+        <v>0.2209</v>
       </c>
       <c r="AY20" s="3" t="n">
-        <v>0.0363</v>
+        <v>0.0414</v>
       </c>
       <c r="AZ20" s="4" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BA20" s="3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BB20" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="BC20" s="3" t="n">
-        <v>85.2</v>
+        <v>81.3</v>
       </c>
       <c r="BD20" s="3" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" s="3" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="BF20" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BG20" s="4" t="inlineStr">
         <is>
@@ -7446,64 +7482,64 @@
         </is>
       </c>
       <c r="BH20" s="3" t="n">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="BJ20" s="3" t="n">
-        <v>0.279</v>
+        <v>0.275</v>
       </c>
       <c r="BK20" s="3" t="n">
-        <v>0.373</v>
+        <v>0.349</v>
       </c>
       <c r="BL20" s="3" t="n">
-        <v>0.598</v>
+        <v>0.497</v>
       </c>
       <c r="BM20" s="3" t="n">
-        <v>0.971</v>
+        <v>0.846</v>
       </c>
       <c r="BN20" s="3" t="n">
-        <v>254</v>
+        <v>101</v>
       </c>
       <c r="BO20" s="3" t="n">
-        <v>1.055</v>
+        <v>1.081</v>
       </c>
       <c r="BP20" s="3" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="BQ20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="BR20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS20" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT20" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="BU20" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BV20" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="BS20" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BT20" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="BU20" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="BV20" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW20" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="BX20" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BY20" s="3" t="n">
-        <v>15.43</v>
+        <v>11.86</v>
       </c>
       <c r="BZ20" s="3" t="n">
-        <v>10.79</v>
+        <v>10.29</v>
       </c>
       <c r="CA20" s="3" t="n">
-        <v>0.275</v>
+        <v>0.286</v>
       </c>
       <c r="CB20" s="4" t="inlineStr">
         <is>
@@ -7511,31 +7547,31 @@
         </is>
       </c>
       <c r="CC20" s="3" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="CD20" s="3" t="n">
-        <v>2.517</v>
+        <v>2.215</v>
       </c>
       <c r="CE20" s="3" t="n">
-        <v>0.2333</v>
+        <v>0.2462</v>
       </c>
       <c r="CF20" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="CG20" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.0462</v>
       </c>
       <c r="CH20" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.1385</v>
       </c>
       <c r="CI20" s="3" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="CJ20" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CK20" s="3" t="n">
-        <v>8.359999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="CL20" s="3" t="n">
         <v>3</v>
@@ -7547,31 +7583,31 @@
         <v>21</v>
       </c>
       <c r="CO20" s="3" t="n">
-        <v>0.137</v>
+        <v>0.1519</v>
       </c>
       <c r="CP20" s="3" t="n">
-        <v>0.0419</v>
+        <v>0.0496</v>
       </c>
       <c r="CQ20" s="3" t="n">
-        <v>0.0042</v>
+        <v>0.0076</v>
       </c>
       <c r="CR20" s="3" t="n">
-        <v>0.0516</v>
+        <v>0.0441</v>
       </c>
       <c r="CS20" s="3" t="n">
-        <v>0.1048</v>
+        <v>0.0856</v>
       </c>
       <c r="CT20" s="3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="CU20" s="3" t="n">
-        <v>0.1335</v>
+        <v>0.1355</v>
       </c>
       <c r="CV20" s="3" t="n">
-        <v>0.1496</v>
+        <v>0.1085</v>
       </c>
       <c r="CW20" s="3" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="CX20" s="4" t="inlineStr">
         <is>
@@ -7593,22 +7629,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>CHC @ CIN</t>
+          <t>CLE @ MIA</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -7622,58 +7658,58 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.07</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>9.81</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>60.7</v>
+        <v>59.8</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>60.7</v>
+        <v>59.8</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>57.3</v>
+        <v>56</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>57.3</v>
+        <v>56</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>50.3</v>
+        <v>48.8</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>50.3</v>
+        <v>48.8</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>45.6</v>
+        <v>43.2</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="Y21" s="7" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Z21" s="7" t="n">
-        <v>42.2</v>
+        <v>43.2</v>
+      </c>
+      <c r="Y21" s="9" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>39.4</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>245.02</v>
+        <v>244.4</v>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
@@ -7682,7 +7718,7 @@
       </c>
       <c r="AC21" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.1 FS | Sim 9.8</t>
+          <t>Forecast 9.6 FS | Sim 9.1</t>
         </is>
       </c>
       <c r="AD21" s="3" t="n">
@@ -7690,26 +7726,28 @@
       </c>
       <c r="AE21" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF21" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AI21" s="4" t="inlineStr">
         <is>
-          <t>1-1-1-1-1-1-1</t>
+          <t>2-1-2-2-3-1-3</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
@@ -7724,7 +7762,7 @@
       </c>
       <c r="AO21" s="4" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="AP21" s="4" t="inlineStr">
@@ -7733,187 +7771,179 @@
         </is>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>4.31</v>
+        <v>3.66</v>
       </c>
       <c r="AR21" s="3" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AS21" s="3" t="n">
-        <v>0.2381</v>
+        <v>0.2108</v>
       </c>
       <c r="AT21" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.0294</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1152</v>
       </c>
       <c r="AV21" s="3" t="n">
-        <v>4.34</v>
+        <v>3.73</v>
       </c>
       <c r="AW21" s="3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AX21" s="3" t="n">
-        <v>0.2209</v>
+        <v>0.2109</v>
       </c>
       <c r="AY21" s="3" t="n">
-        <v>0.0414</v>
+        <v>0.0305</v>
       </c>
       <c r="AZ21" s="4" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BA21" s="3" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="BB21" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC21" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="BD21" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE21" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="BF21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC21" s="4" t="n"/>
+      <c r="BD21" s="4" t="n"/>
+      <c r="BE21" s="4" t="n"/>
+      <c r="BF21" s="4" t="n"/>
+      <c r="BG21" s="4" t="inlineStr">
+        <is>
+          <t>Indoor/retractable neutral</t>
+        </is>
+      </c>
+      <c r="BH21" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="BI21" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="BJ21" s="3" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BK21" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BL21" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BM21" s="3" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="BN21" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="BO21" s="3" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="BP21" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="BQ21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BR21" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="BH21" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="BI21" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="BJ21" s="3" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="BK21" s="3" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="BL21" s="3" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="BM21" s="3" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="BN21" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="BO21" s="3" t="n">
-        <v>1.081</v>
-      </c>
-      <c r="BP21" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="BQ21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR21" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="BS21" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BT21" s="3" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="BU21" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BV21" s="3" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="BW21" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BX21" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BY21" s="3" t="n">
-        <v>11.86</v>
+        <v>12.71</v>
       </c>
       <c r="BZ21" s="3" t="n">
-        <v>10.29</v>
+        <v>11.36</v>
       </c>
       <c r="CA21" s="3" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="CB21" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="CC21" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>11.47</v>
       </c>
       <c r="CD21" s="3" t="n">
-        <v>2.215</v>
+        <v>2.446</v>
       </c>
       <c r="CE21" s="3" t="n">
-        <v>0.2462</v>
+        <v>0.3077</v>
       </c>
       <c r="CF21" s="3" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1692</v>
       </c>
       <c r="CG21" s="3" t="n">
         <v>0.0462</v>
       </c>
       <c r="CH21" s="3" t="n">
-        <v>0.1385</v>
+        <v>0.0615</v>
       </c>
       <c r="CI21" s="3" t="n">
-        <v>0.0615</v>
+        <v>0.0154</v>
       </c>
       <c r="CJ21" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK21" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="CL21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="CM21" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CN21" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CO21" s="3" t="n">
-        <v>0.1519</v>
+        <v>0.1649</v>
       </c>
       <c r="CP21" s="3" t="n">
-        <v>0.0496</v>
+        <v>0.0521</v>
       </c>
       <c r="CQ21" s="3" t="n">
-        <v>0.0076</v>
+        <v>0.0089</v>
       </c>
       <c r="CR21" s="3" t="n">
-        <v>0.0441</v>
+        <v>0.0269</v>
       </c>
       <c r="CS21" s="3" t="n">
-        <v>0.0856</v>
+        <v>0.0839</v>
       </c>
       <c r="CT21" s="3" t="n">
-        <v>0.0081</v>
+        <v>0.0114</v>
       </c>
       <c r="CU21" s="3" t="n">
-        <v>0.1355</v>
+        <v>0.1412</v>
       </c>
       <c r="CV21" s="3" t="n">
-        <v>0.1085</v>
+        <v>0.1018</v>
       </c>
       <c r="CW21" s="3" t="n">
-        <v>0.023</v>
+        <v>0.0213</v>
       </c>
       <c r="CX21" s="4" t="inlineStr">
         <is>
@@ -7967,55 +7997,55 @@
         <v>10.2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10.38</v>
+        <v>10.31</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>85.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>76</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>76</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>63.1</v>
+        <v>63.4</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>63.1</v>
+        <v>63.4</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>58.5</v>
+        <v>59.3</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>58.5</v>
+        <v>59.3</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="V22" s="7" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
       <c r="X22" s="7" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
       <c r="Y22" s="7" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="Z22" s="7" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>244.45</v>
+        <v>244.17</v>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
@@ -8024,7 +8054,7 @@
       </c>
       <c r="AC22" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.2 FS | Sim 10.4</t>
+          <t>Forecast 10.2 FS | Sim 10.3</t>
         </is>
       </c>
       <c r="AD22" s="3" t="n">
@@ -8032,10 +8062,12 @@
       </c>
       <c r="AE22" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF22" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AG22" s="3" t="n">
         <v>6</v>
       </c>
@@ -8211,13 +8243,13 @@
         <v>8</v>
       </c>
       <c r="CK22" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="CL22" s="3" t="n">
         <v>4</v>
       </c>
       <c r="CM22" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CN22" s="3" t="n">
         <v>22</v>
@@ -8269,22 +8301,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>CLE @ MIA</t>
+          <t>CHC @ CIN</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -8294,62 +8326,62 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.56</v>
+        <v>9.98</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>8.99</v>
+        <v>9.59</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>82</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>73.7</v>
+        <v>72.3</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>73.7</v>
+        <v>72.3</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="T23" s="7" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>42.4</v>
+        <v>43.4</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>42.4</v>
+        <v>43.4</v>
       </c>
       <c r="Y23" s="9" t="n">
-        <v>38.6</v>
+        <v>39.9</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>38.6</v>
+        <v>39.9</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>242.11</v>
+        <v>240.15</v>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
@@ -8358,7 +8390,7 @@
       </c>
       <c r="AC23" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.6 FS | Sim 9.0</t>
+          <t>Forecast 10.0 FS | Sim 9.6</t>
         </is>
       </c>
       <c r="AD23" s="3" t="n">
@@ -8366,10 +8398,12 @@
       </c>
       <c r="AE23" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF23" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG23" s="3" t="n">
         <v>2</v>
       </c>
@@ -8378,11 +8412,11 @@
       </c>
       <c r="AI23" s="4" t="inlineStr">
         <is>
-          <t>2-1-2-2-3-1-3</t>
+          <t>2-2-2-2-2-2-2</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>5.02</v>
@@ -8400,7 +8434,7 @@
       </c>
       <c r="AO23" s="4" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="AP23" s="4" t="inlineStr">
@@ -8409,179 +8443,187 @@
         </is>
       </c>
       <c r="AQ23" s="3" t="n">
-        <v>3.66</v>
+        <v>4.31</v>
       </c>
       <c r="AR23" s="3" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AS23" s="3" t="n">
-        <v>0.2108</v>
+        <v>0.2381</v>
       </c>
       <c r="AT23" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.0238</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>0.1152</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AV23" s="3" t="n">
-        <v>3.73</v>
+        <v>4.34</v>
       </c>
       <c r="AW23" s="3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AX23" s="3" t="n">
-        <v>0.2109</v>
+        <v>0.2209</v>
       </c>
       <c r="AY23" s="3" t="n">
-        <v>0.0305</v>
+        <v>0.0414</v>
       </c>
       <c r="AZ23" s="4" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BA23" s="3" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="BB23" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="BD23" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE23" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="BF23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG23" s="4" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BH23" s="3" t="n">
+        <v>409</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="BJ23" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="BK23" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BL23" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="BM23" s="3" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="BN23" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO23" s="3" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="BP23" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="BQ23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BV23" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="BC23" s="4" t="n"/>
-      <c r="BD23" s="4" t="n"/>
-      <c r="BE23" s="4" t="n"/>
-      <c r="BF23" s="4" t="n"/>
-      <c r="BG23" s="4" t="inlineStr">
-        <is>
-          <t>Indoor/retractable neutral</t>
-        </is>
-      </c>
-      <c r="BH23" s="3" t="n">
-        <v>405</v>
-      </c>
-      <c r="BI23" s="3" t="n">
-        <v>375</v>
-      </c>
-      <c r="BJ23" s="3" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="BK23" s="3" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="BL23" s="3" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="BM23" s="3" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="BN23" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="BO23" s="3" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="BP23" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="BQ23" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BR23" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BS23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT23" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="BU23" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="BV23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW23" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="BX23" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BY23" s="3" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BZ23" s="3" t="n">
-        <v>11.36</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="CA23" s="3" t="n">
-        <v>0.333</v>
+        <v>0.293</v>
       </c>
       <c r="CB23" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="CC23" s="3" t="n">
-        <v>11.47</v>
+        <v>8.9</v>
       </c>
       <c r="CD23" s="3" t="n">
-        <v>2.446</v>
+        <v>2.194</v>
       </c>
       <c r="CE23" s="3" t="n">
-        <v>0.3077</v>
+        <v>0.2742</v>
       </c>
       <c r="CF23" s="3" t="n">
-        <v>0.1692</v>
+        <v>0.1452</v>
       </c>
       <c r="CG23" s="3" t="n">
-        <v>0.0462</v>
+        <v>0.0806</v>
       </c>
       <c r="CH23" s="3" t="n">
-        <v>0.0615</v>
+        <v>0.0484</v>
       </c>
       <c r="CI23" s="3" t="n">
-        <v>0.0154</v>
+        <v>0</v>
       </c>
       <c r="CJ23" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK23" s="3" t="n">
-        <v>7.43</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CL23" s="3" t="n">
         <v>3</v>
       </c>
       <c r="CM23" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CN23" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CO23" s="3" t="n">
-        <v>0.1649</v>
+        <v>0.1431</v>
       </c>
       <c r="CP23" s="3" t="n">
-        <v>0.0521</v>
+        <v>0.0566</v>
       </c>
       <c r="CQ23" s="3" t="n">
-        <v>0.0089</v>
+        <v>0.003</v>
       </c>
       <c r="CR23" s="3" t="n">
-        <v>0.0269</v>
+        <v>0.047</v>
       </c>
       <c r="CS23" s="3" t="n">
-        <v>0.0839</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="CT23" s="3" t="n">
-        <v>0.0114</v>
+        <v>0.0065</v>
       </c>
       <c r="CU23" s="3" t="n">
-        <v>0.1387</v>
+        <v>0.1254</v>
       </c>
       <c r="CV23" s="3" t="n">
-        <v>0.116</v>
+        <v>0.1367</v>
       </c>
       <c r="CW23" s="3" t="n">
-        <v>0.0213</v>
+        <v>0.0148</v>
       </c>
       <c r="CX23" s="4" t="inlineStr">
         <is>
@@ -8603,22 +8645,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>CHC @ CIN</t>
+          <t>ATL @ STL</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -8628,62 +8670,62 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
         <v>9.98</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>72.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>72.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>69.3</v>
+        <v>63.2</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>55.8</v>
+        <v>63.2</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>50.8</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>55.8</v>
+        <v>50.8</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>48.9</v>
+        <v>44.4</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>48.9</v>
+        <v>44.4</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>44</v>
+        <v>40.9</v>
       </c>
       <c r="X24" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y24" s="7" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="Z24" s="7" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>38.2</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>240.78</v>
+        <v>239.58</v>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
@@ -8692,34 +8734,36 @@
       </c>
       <c r="AC24" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.0 FS | Sim 9.6</t>
+          <t>Forecast 10.0 FS | Sim 9.3</t>
         </is>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE24" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF24" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AG24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH24" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AI24" s="4" t="inlineStr">
         <is>
-          <t>2-2-2-2-2-2-2</t>
+          <t>4-3-4-3-3-4-3</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="AL24" s="4" t="inlineStr">
         <is>
@@ -8734,7 +8778,7 @@
       </c>
       <c r="AO24" s="4" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Danny Young</t>
         </is>
       </c>
       <c r="AP24" s="4" t="inlineStr">
@@ -8743,54 +8787,54 @@
         </is>
       </c>
       <c r="AQ24" s="3" t="n">
-        <v>4.31</v>
+        <v>2.7</v>
       </c>
       <c r="AR24" s="3" t="n">
-        <v>1.31</v>
+        <v>0.9</v>
       </c>
       <c r="AS24" s="3" t="n">
-        <v>0.2381</v>
+        <v>0.1667</v>
       </c>
       <c r="AT24" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.0833</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="AV24" s="3" t="n">
-        <v>4.34</v>
+        <v>3.61</v>
       </c>
       <c r="AW24" s="3" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AX24" s="3" t="n">
-        <v>0.2209</v>
+        <v>0.2043</v>
       </c>
       <c r="AY24" s="3" t="n">
-        <v>0.0414</v>
+        <v>0.0305</v>
       </c>
       <c r="AZ24" s="4" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BA24" s="3" t="n">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="BB24" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="BC24" s="3" t="n">
-        <v>81.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="BD24" s="3" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" s="3" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="BF24" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BG24" s="4" t="inlineStr">
         <is>
@@ -8798,96 +8842,96 @@
         </is>
       </c>
       <c r="BH24" s="3" t="n">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="BJ24" s="3" t="n">
-        <v>0.256</v>
+        <v>0.294</v>
       </c>
       <c r="BK24" s="3" t="n">
-        <v>0.337</v>
+        <v>0.353</v>
       </c>
       <c r="BL24" s="3" t="n">
-        <v>0.474</v>
+        <v>0.534</v>
       </c>
       <c r="BM24" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.887</v>
       </c>
       <c r="BN24" s="3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BO24" s="3" t="n">
-        <v>0.903</v>
+        <v>0.959</v>
       </c>
       <c r="BP24" s="3" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="BQ24" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BR24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="BS24" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BT24" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU24" s="3" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="BV24" s="3" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="BW24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BX24" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BY24" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="BZ24" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>11.93</v>
       </c>
       <c r="CA24" s="3" t="n">
-        <v>0.293</v>
+        <v>0.319</v>
       </c>
       <c r="CB24" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="CC24" s="3" t="n">
-        <v>8.9</v>
+        <v>8.77</v>
       </c>
       <c r="CD24" s="3" t="n">
-        <v>2.194</v>
+        <v>2.93</v>
       </c>
       <c r="CE24" s="3" t="n">
-        <v>0.2742</v>
+        <v>0.2632</v>
       </c>
       <c r="CF24" s="3" t="n">
-        <v>0.1452</v>
+        <v>0.1228</v>
       </c>
       <c r="CG24" s="3" t="n">
-        <v>0.0806</v>
+        <v>0.0702</v>
       </c>
       <c r="CH24" s="3" t="n">
-        <v>0.0484</v>
+        <v>0.1404</v>
       </c>
       <c r="CI24" s="3" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="CJ24" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK24" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="CL24" s="3" t="n">
         <v>3</v>
@@ -8899,31 +8943,31 @@
         <v>21</v>
       </c>
       <c r="CO24" s="3" t="n">
-        <v>0.1431</v>
+        <v>0.1138</v>
       </c>
       <c r="CP24" s="3" t="n">
-        <v>0.0566</v>
+        <v>0.0357</v>
       </c>
       <c r="CQ24" s="3" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="CR24" s="3" t="n">
-        <v>0.047</v>
+        <v>0.0596</v>
       </c>
       <c r="CS24" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="CT24" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="CU24" s="3" t="n">
-        <v>0.1254</v>
+        <v>0.1365</v>
       </c>
       <c r="CV24" s="3" t="n">
-        <v>0.1367</v>
+        <v>0.1656</v>
       </c>
       <c r="CW24" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.0181</v>
       </c>
       <c r="CX24" s="4" t="inlineStr">
         <is>
@@ -8977,55 +9021,55 @@
         <v>9.74</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>9.4</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>78.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>57</v>
+        <v>57.7</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>57</v>
+        <v>57.7</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>41.9</v>
+        <v>42.5</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>41.9</v>
+        <v>42.5</v>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>236.69</v>
+        <v>237.84</v>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
@@ -9034,7 +9078,7 @@
       </c>
       <c r="AC25" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.7 FS | Sim 9.4</t>
+          <t>Forecast 9.7 FS | Sim 9.5</t>
         </is>
       </c>
       <c r="AD25" s="3" t="n">
@@ -9042,10 +9086,12 @@
       </c>
       <c r="AE25" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF25" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG25" s="3" t="n">
         <v>2</v>
       </c>
@@ -9221,7 +9267,7 @@
         <v>7</v>
       </c>
       <c r="CK25" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CL25" s="3" t="n">
         <v>3</v>
@@ -9311,46 +9357,46 @@
         <v>9.23</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8.44</v>
+        <v>8.42</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="T26" s="7" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="V26" s="7" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="X26" s="9" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>34.1</v>
@@ -9359,7 +9405,7 @@
         <v>34.1</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>236.47</v>
+        <v>236.26</v>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
@@ -9457,16 +9503,16 @@
         <v>1.01</v>
       </c>
       <c r="BC26" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD26" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE26" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG26" s="4" t="inlineStr">
         <is>
@@ -9563,7 +9609,7 @@
         <v>6</v>
       </c>
       <c r="CK26" s="3" t="n">
-        <v>7.74</v>
+        <v>7.71</v>
       </c>
       <c r="CL26" s="3" t="n">
         <v>3</v>
@@ -9621,7 +9667,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -9646,62 +9692,62 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.99</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>56.6</v>
+        <v>55.7</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>56.6</v>
+        <v>55.7</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>52.7</v>
+        <v>51.8</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>52.7</v>
+        <v>51.8</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="Z27" s="9" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>235.42</v>
+        <v>236.18</v>
       </c>
       <c r="AB27" s="4" t="inlineStr">
         <is>
@@ -9710,11 +9756,11 @@
       </c>
       <c r="AC27" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.0 FS | Sim 8.5</t>
+          <t>Forecast 9.3 FS | Sim 8.4</t>
         </is>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
@@ -9723,21 +9769,21 @@
       </c>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI27" s="4" t="inlineStr">
         <is>
-          <t>5-2-2-5-2-6</t>
+          <t>1-1-1-1-6-7-1</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>4.94</v>
+        <v>5.04</v>
       </c>
       <c r="AL27" s="4" t="inlineStr">
         <is>
@@ -9745,7 +9791,7 @@
         </is>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN27" s="3" t="n">
         <v>1.04</v>
@@ -9799,16 +9845,16 @@
         <v>1.01</v>
       </c>
       <c r="BC27" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD27" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE27" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG27" s="4" t="inlineStr">
         <is>
@@ -9816,96 +9862,96 @@
         </is>
       </c>
       <c r="BH27" s="3" t="n">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BJ27" s="3" t="n">
-        <v>0.266</v>
+        <v>0.301</v>
       </c>
       <c r="BK27" s="3" t="n">
-        <v>0.364</v>
+        <v>0.344</v>
       </c>
       <c r="BL27" s="3" t="n">
-        <v>0.445</v>
+        <v>0.507</v>
       </c>
       <c r="BM27" s="3" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.851</v>
       </c>
       <c r="BN27" s="3" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="BO27" s="3" t="n">
-        <v>0.826</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="BP27" s="3" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="BQ27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="BR27" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BS27" s="3" t="n">
         <v>9</v>
       </c>
       <c r="BT27" s="3" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="BU27" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="BV27" s="3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="BW27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="BX27" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BY27" s="3" t="n">
-        <v>11.57</v>
+        <v>7</v>
       </c>
       <c r="BZ27" s="3" t="n">
-        <v>11.43</v>
+        <v>10.29</v>
       </c>
       <c r="CA27" s="3" t="n">
-        <v>0.327</v>
+        <v>0.283</v>
       </c>
       <c r="CB27" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="CC27" s="3" t="n">
-        <v>9.1</v>
+        <v>10.17</v>
       </c>
       <c r="CD27" s="3" t="n">
-        <v>2.667</v>
+        <v>2.441</v>
       </c>
       <c r="CE27" s="3" t="n">
-        <v>0.2667</v>
+        <v>0.2542</v>
       </c>
       <c r="CF27" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1356</v>
       </c>
       <c r="CG27" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.0508</v>
       </c>
       <c r="CH27" s="3" t="n">
-        <v>0.15</v>
+        <v>0.0508</v>
       </c>
       <c r="CI27" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.0169</v>
       </c>
       <c r="CJ27" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK27" s="3" t="n">
-        <v>7.05</v>
+        <v>7.18</v>
       </c>
       <c r="CL27" s="3" t="n">
         <v>3</v>
@@ -9917,31 +9963,31 @@
         <v>19</v>
       </c>
       <c r="CO27" s="3" t="n">
-        <v>0.1483</v>
+        <v>0.1596</v>
       </c>
       <c r="CP27" s="3" t="n">
-        <v>0.0506</v>
+        <v>0.0539</v>
       </c>
       <c r="CQ27" s="3" t="n">
-        <v>0.0058</v>
+        <v>0.0091</v>
       </c>
       <c r="CR27" s="3" t="n">
-        <v>0.0246</v>
+        <v>0.0229</v>
       </c>
       <c r="CS27" s="3" t="n">
-        <v>0.1082</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="CT27" s="3" t="n">
-        <v>0.0118</v>
+        <v>0.0114</v>
       </c>
       <c r="CU27" s="3" t="n">
-        <v>0.1427</v>
+        <v>0.1269</v>
       </c>
       <c r="CV27" s="3" t="n">
-        <v>0.1245</v>
+        <v>0.1382</v>
       </c>
       <c r="CW27" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.02</v>
       </c>
       <c r="CX27" s="4" t="inlineStr">
         <is>
@@ -9995,55 +10041,55 @@
         <v>9.449999999999999</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>66.7</v>
+        <v>65.7</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>66.7</v>
+        <v>65.7</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="V28" s="7" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="X28" s="7" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="Y28" s="9" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>235.38</v>
+        <v>234.34</v>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
@@ -10052,7 +10098,7 @@
       </c>
       <c r="AC28" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.4 FS | Sim 9.4</t>
+          <t>Forecast 9.4 FS | Sim 9.3</t>
         </is>
       </c>
       <c r="AD28" s="3" t="n">
@@ -10239,7 +10285,7 @@
         <v>7</v>
       </c>
       <c r="CK28" s="3" t="n">
-        <v>8.41</v>
+        <v>8.35</v>
       </c>
       <c r="CL28" s="3" t="n">
         <v>3</v>
@@ -10297,7 +10343,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -10322,62 +10368,62 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.279999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>69.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>69.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>66.3</v>
+        <v>67.3</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>66.3</v>
+        <v>67.3</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>235.23</v>
+        <v>234.3</v>
       </c>
       <c r="AB29" s="4" t="inlineStr">
         <is>
@@ -10386,11 +10432,11 @@
       </c>
       <c r="AC29" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.3 FS | Sim 8.3</t>
+          <t>Forecast 9.0 FS | Sim 8.4</t>
         </is>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" s="4" t="inlineStr">
         <is>
@@ -10399,21 +10445,21 @@
       </c>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI29" s="4" t="inlineStr">
         <is>
-          <t>1-1-1-1-6-7-1</t>
+          <t>5-2-2-5-2-6</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>5.04</v>
+        <v>4.94</v>
       </c>
       <c r="AL29" s="4" t="inlineStr">
         <is>
@@ -10421,7 +10467,7 @@
         </is>
       </c>
       <c r="AM29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN29" s="3" t="n">
         <v>1.04</v>
@@ -10475,16 +10521,16 @@
         <v>1.01</v>
       </c>
       <c r="BC29" s="3" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="BD29" s="3" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="BF29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG29" s="4" t="inlineStr">
         <is>
@@ -10492,96 +10538,96 @@
         </is>
       </c>
       <c r="BH29" s="3" t="n">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="BJ29" s="3" t="n">
-        <v>0.301</v>
+        <v>0.266</v>
       </c>
       <c r="BK29" s="3" t="n">
-        <v>0.344</v>
+        <v>0.364</v>
       </c>
       <c r="BL29" s="3" t="n">
-        <v>0.507</v>
+        <v>0.445</v>
       </c>
       <c r="BM29" s="3" t="n">
-        <v>0.851</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="BN29" s="3" t="n">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="BO29" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="BP29" s="3" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="BQ29" s="3" t="n">
         <v>18</v>
       </c>
       <c r="BR29" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BS29" s="3" t="n">
         <v>9</v>
       </c>
       <c r="BT29" s="3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="BU29" s="3" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="BV29" s="3" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="BW29" s="3" t="n">
         <v>3</v>
       </c>
       <c r="BX29" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BY29" s="3" t="n">
-        <v>7</v>
+        <v>11.57</v>
       </c>
       <c r="BZ29" s="3" t="n">
-        <v>10.29</v>
+        <v>11.43</v>
       </c>
       <c r="CA29" s="3" t="n">
-        <v>0.283</v>
+        <v>0.327</v>
       </c>
       <c r="CB29" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="CC29" s="3" t="n">
-        <v>10.17</v>
+        <v>9.1</v>
       </c>
       <c r="CD29" s="3" t="n">
-        <v>2.441</v>
+        <v>2.667</v>
       </c>
       <c r="CE29" s="3" t="n">
-        <v>0.2542</v>
+        <v>0.2667</v>
       </c>
       <c r="CF29" s="3" t="n">
-        <v>0.1356</v>
+        <v>0.15</v>
       </c>
       <c r="CG29" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.0667</v>
       </c>
       <c r="CH29" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.15</v>
       </c>
       <c r="CI29" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.0167</v>
       </c>
       <c r="CJ29" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK29" s="3" t="n">
-        <v>7.09</v>
+        <v>7.05</v>
       </c>
       <c r="CL29" s="3" t="n">
         <v>3</v>
@@ -10593,31 +10639,31 @@
         <v>19</v>
       </c>
       <c r="CO29" s="3" t="n">
-        <v>0.1596</v>
+        <v>0.1483</v>
       </c>
       <c r="CP29" s="3" t="n">
-        <v>0.0539</v>
+        <v>0.0506</v>
       </c>
       <c r="CQ29" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.0058</v>
       </c>
       <c r="CR29" s="3" t="n">
-        <v>0.0229</v>
+        <v>0.0246</v>
       </c>
       <c r="CS29" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.1082</v>
       </c>
       <c r="CT29" s="3" t="n">
-        <v>0.0114</v>
+        <v>0.0118</v>
       </c>
       <c r="CU29" s="3" t="n">
-        <v>0.1269</v>
+        <v>0.1427</v>
       </c>
       <c r="CV29" s="3" t="n">
-        <v>0.1382</v>
+        <v>0.1245</v>
       </c>
       <c r="CW29" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0111</v>
       </c>
       <c r="CX29" s="4" t="inlineStr">
         <is>
@@ -10639,87 +10685,87 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Kyle Higashioka</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>HOU @ TEX</t>
+          <t>LAA @ MIN</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.29</v>
+        <v>9.49</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>10.91</v>
+        <v>9.35</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>86.7</v>
+        <v>79.5</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>80</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>80</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>76.2</v>
+        <v>67</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>76.2</v>
+        <v>67</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U30" s="6" t="n">
-        <v>55.4</v>
+        <v>58.7</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="T30" s="7" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <v>46.8</v>
       </c>
       <c r="V30" s="7" t="n">
-        <v>55.4</v>
+        <v>46.8</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>50.1</v>
+        <v>43</v>
       </c>
       <c r="X30" s="7" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="Y30" s="7" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="Z30" s="7" t="n">
-        <v>45.9</v>
+        <v>43</v>
+      </c>
+      <c r="Y30" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>38.3</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>234.87</v>
+        <v>234.22</v>
       </c>
       <c r="AB30" s="4" t="inlineStr">
         <is>
@@ -10728,49 +10774,51 @@
       </c>
       <c r="AC30" s="8" t="inlineStr">
         <is>
-          <t>Forecast 10.3 FS | Sim 10.9</t>
+          <t>Forecast 9.5 FS | Sim 9.3</t>
         </is>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF30" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AG30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" s="3" t="n">
         <v>3</v>
       </c>
       <c r="AI30" s="4" t="inlineStr">
         <is>
-          <t>9-1-1</t>
+          <t>2-2-2</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>4.85</v>
+        <v>5.02</v>
       </c>
       <c r="AL30" s="4" t="inlineStr">
         <is>
-          <t>Likely regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="AM30" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AN30" s="3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AO30" s="4" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="AP30" s="4" t="inlineStr">
@@ -10779,183 +10827,191 @@
         </is>
       </c>
       <c r="AQ30" s="3" t="n">
-        <v>10.22</v>
+        <v>3.67</v>
       </c>
       <c r="AR30" s="3" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AS30" s="3" t="n">
-        <v>0.254</v>
+        <v>0.196</v>
       </c>
       <c r="AT30" s="3" t="n">
-        <v>0.0476</v>
+        <v>0.0323</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="AV30" s="3" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="AW30" s="3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AX30" s="3" t="n">
-        <v>0.2086</v>
+        <v>0.2213</v>
       </c>
       <c r="AY30" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0305</v>
       </c>
       <c r="AZ30" s="4" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BA30" s="3" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="BB30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC30" s="4" t="n"/>
-      <c r="BD30" s="4" t="n"/>
-      <c r="BE30" s="4" t="n"/>
-      <c r="BF30" s="4" t="n"/>
+        <v>1.055</v>
+      </c>
+      <c r="BC30" s="3" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="BD30" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE30" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="BF30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="BG30" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="BH30" s="3" t="n">
-        <v>173</v>
+        <v>350</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>155</v>
+        <v>279</v>
       </c>
       <c r="BJ30" s="3" t="n">
-        <v>0.219</v>
+        <v>0.233</v>
       </c>
       <c r="BK30" s="3" t="n">
-        <v>0.301</v>
+        <v>0.389</v>
       </c>
       <c r="BL30" s="3" t="n">
-        <v>0.355</v>
+        <v>0.473</v>
       </c>
       <c r="BM30" s="3" t="n">
-        <v>0.656</v>
+        <v>0.862</v>
       </c>
       <c r="BN30" s="3" t="n">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="BO30" s="3" t="n">
-        <v>0.63</v>
+        <v>0.863</v>
       </c>
       <c r="BP30" s="3" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BQ30" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BR30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="BS30" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BT30" s="3" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="BU30" s="3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="BV30" s="3" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="BW30" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BX30" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BY30" s="3" t="n">
-        <v>4</v>
+        <v>12.57</v>
       </c>
       <c r="BZ30" s="3" t="n">
-        <v>3.43</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="CA30" s="3" t="n">
-        <v>0.175</v>
+        <v>0.224</v>
       </c>
       <c r="CB30" s="4" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="CC30" s="3" t="n">
-        <v>5.03</v>
+        <v>9.5</v>
       </c>
       <c r="CD30" s="3" t="n">
-        <v>1.067</v>
+        <v>2.076</v>
       </c>
       <c r="CE30" s="3" t="n">
-        <v>0.1556</v>
+        <v>0.197</v>
       </c>
       <c r="CF30" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.1061</v>
       </c>
       <c r="CG30" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.0606</v>
       </c>
       <c r="CH30" s="3" t="n">
-        <v>0.1111</v>
+        <v>0.1061</v>
       </c>
       <c r="CI30" s="3" t="n">
-        <v>0</v>
+        <v>0.0303</v>
       </c>
       <c r="CJ30" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CK30" s="3" t="n">
-        <v>8.59</v>
+        <v>7.99</v>
       </c>
       <c r="CL30" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CM30" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CN30" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CO30" s="3" t="n">
-        <v>0.1817</v>
+        <v>0.107</v>
       </c>
       <c r="CP30" s="3" t="n">
-        <v>0.0427</v>
+        <v>0.0395</v>
       </c>
       <c r="CQ30" s="3" t="n">
-        <v>0.0039</v>
+        <v>0.0023</v>
       </c>
       <c r="CR30" s="3" t="n">
-        <v>0.0547</v>
+        <v>0.0457</v>
       </c>
       <c r="CS30" s="3" t="n">
-        <v>0.1238</v>
+        <v>0.1502</v>
       </c>
       <c r="CT30" s="3" t="n">
         <v>0.0129</v>
       </c>
       <c r="CU30" s="3" t="n">
-        <v>0.1334</v>
+        <v>0.1384</v>
       </c>
       <c r="CV30" s="3" t="n">
-        <v>0.0998</v>
+        <v>0.1102</v>
       </c>
       <c r="CW30" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0145</v>
       </c>
       <c r="CX30" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10973,22 +11029,22 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>LAA @ MIN</t>
+          <t>CHC @ CIN</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -10998,62 +11054,62 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.49</v>
+        <v>9.81</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>78.8</v>
+        <v>82.2</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>58.1</v>
+        <v>59.4</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>58.1</v>
+        <v>59.4</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>53.4</v>
+        <v>55.2</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>53.4</v>
+        <v>55.2</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>45.7</v>
+        <v>47.5</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>45.7</v>
+        <v>47.5</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="Y31" s="9" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>234.42</v>
+        <v>233.4</v>
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
@@ -11062,34 +11118,36 @@
       </c>
       <c r="AC31" s="8" t="inlineStr">
         <is>
-          <t>Forecast 9.5 FS | Sim 9.4</t>
+          <t>Forecast 9.8 FS | Sim 9.4</t>
         </is>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE31" s="4" t="inlineStr">
         <is>
-          <t>Last 7 Confirmed</t>
-        </is>
-      </c>
-      <c r="AF31" s="4" t="n"/>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AG31" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI31" s="4" t="inlineStr">
         <is>
-          <t>2-2-2</t>
+          <t>4-8-4-8-4</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>5.02</v>
+        <v>4.73</v>
       </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
@@ -11097,135 +11155,135 @@
         </is>
       </c>
       <c r="AM31" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN31" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="AO31" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="AP31" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="AR31" s="3" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AS31" s="3" t="n">
-        <v>0.196</v>
+        <v>0.2215</v>
       </c>
       <c r="AT31" s="3" t="n">
-        <v>0.0323</v>
+        <v>0.0365</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="AV31" s="3" t="n">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="AW31" s="3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AX31" s="3" t="n">
-        <v>0.2213</v>
+        <v>0.2126</v>
       </c>
       <c r="AY31" s="3" t="n">
-        <v>0.0305</v>
+        <v>0.0341</v>
       </c>
       <c r="AZ31" s="4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BA31" s="3" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="BB31" s="3" t="n">
-        <v>1.055</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" s="3" t="n">
-        <v>91.7</v>
+        <v>81.3</v>
       </c>
       <c r="BD31" s="3" t="n">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>233</v>
+        <v>72</v>
       </c>
       <c r="BF31" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG31" s="4" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="BH31" s="3" t="n">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>279</v>
+        <v>216</v>
       </c>
       <c r="BJ31" s="3" t="n">
-        <v>0.233</v>
+        <v>0.278</v>
       </c>
       <c r="BK31" s="3" t="n">
-        <v>0.389</v>
+        <v>0.366</v>
       </c>
       <c r="BL31" s="3" t="n">
-        <v>0.473</v>
+        <v>0.407</v>
       </c>
       <c r="BM31" s="3" t="n">
-        <v>0.862</v>
+        <v>0.773</v>
       </c>
       <c r="BN31" s="3" t="n">
-        <v>263</v>
+        <v>91</v>
       </c>
       <c r="BO31" s="3" t="n">
-        <v>0.863</v>
+        <v>0.975</v>
       </c>
       <c r="BP31" s="3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BQ31" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BR31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="BS31" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BT31" s="3" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="BU31" s="3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="BV31" s="3" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="BW31" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BX31" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BY31" s="3" t="n">
-        <v>12.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BZ31" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="CA31" s="3" t="n">
-        <v>0.224</v>
+        <v>0.279</v>
       </c>
       <c r="CB31" s="4" t="inlineStr">
         <is>
@@ -11233,31 +11291,31 @@
         </is>
       </c>
       <c r="CC31" s="3" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="CD31" s="3" t="n">
-        <v>2.076</v>
+        <v>2.472</v>
       </c>
       <c r="CE31" s="3" t="n">
-        <v>0.197</v>
+        <v>0.2264</v>
       </c>
       <c r="CF31" s="3" t="n">
-        <v>0.1061</v>
+        <v>0.1132</v>
       </c>
       <c r="CG31" s="3" t="n">
-        <v>0.0606</v>
+        <v>0.0566</v>
       </c>
       <c r="CH31" s="3" t="n">
-        <v>0.1061</v>
+        <v>0.1887</v>
       </c>
       <c r="CI31" s="3" t="n">
-        <v>0.0303</v>
+        <v>0</v>
       </c>
       <c r="CJ31" s="3" t="n">
         <v>7</v>
       </c>
       <c r="CK31" s="3" t="n">
-        <v>8.26</v>
+        <v>7.81</v>
       </c>
       <c r="CL31" s="3" t="n">
         <v>3</v>
@@ -11269,31 +11327,31 @@
         <v>21</v>
       </c>
       <c r="CO31" s="3" t="n">
-        <v>0.107</v>
+        <v>0.1521</v>
       </c>
       <c r="CP31" s="3" t="n">
-        <v>0.0395</v>
+        <v>0.0508</v>
       </c>
       <c r="CQ31" s="3" t="n">
-        <v>0.0023</v>
+        <v>0.0031</v>
       </c>
       <c r="CR31" s="3" t="n">
-        <v>0.0457</v>
+        <v>0.0428</v>
       </c>
       <c r="CS31" s="3" t="n">
-        <v>0.1502</v>
+        <v>0.1304</v>
       </c>
       <c r="CT31" s="3" t="n">
-        <v>0.0129</v>
+        <v>0.0127</v>
       </c>
       <c r="CU31" s="3" t="n">
-        <v>0.1384</v>
+        <v>0.1339</v>
       </c>
       <c r="CV31" s="3" t="n">
-        <v>0.1102</v>
+        <v>0.1565</v>
       </c>
       <c r="CW31" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.0086</v>
       </c>
       <c r="CX31" s="4" t="inlineStr">
         <is>
